--- a/research/traditional_assets/database/data/chile/chile_oil_gas_distribution.xlsx
+++ b/research/traditional_assets/database/data/chile/chile_oil_gas_distribution.xlsx
@@ -1278,7 +1278,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1415,22 +1415,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.07670915467234132</v>
+        <v>0.076534889954726</v>
       </c>
       <c r="C2">
-        <v>866.9255716940827</v>
+        <v>860.5720288128888</v>
       </c>
       <c r="D2">
-        <v>738.1255716940827</v>
+        <v>740.9030288128887</v>
       </c>
       <c r="E2">
-        <v>-428.4</v>
+        <v>-419.269</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>9.130999999999998</v>
       </c>
       <c r="G2">
         <v>128.8</v>
@@ -1451,28 +1451,28 @@
         <v>147.1</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.4592892999999999</v>
       </c>
       <c r="N2">
-        <v>147.1</v>
+        <v>146.6407107</v>
       </c>
       <c r="O2">
-        <v>39.71699999999999</v>
+        <v>39.592991889</v>
       </c>
       <c r="P2">
-        <v>107.383</v>
+        <v>107.047718811</v>
       </c>
       <c r="Q2">
-        <v>134.783</v>
+        <v>134.447718811</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.07670915467234132</v>
+        <v>0.0769370706613394</v>
       </c>
       <c r="T2">
-        <v>0.5661120226706919</v>
+        <v>0.5702863840499809</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1489,7 +1489,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>320.2774373363368</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1497,22 +1497,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.076534889954726</v>
+        <v>0.07636062523711068</v>
       </c>
       <c r="C3">
-        <v>860.5720288128888</v>
+        <v>854.2394672000053</v>
       </c>
       <c r="D3">
-        <v>740.9030288128887</v>
+        <v>743.7014672000053</v>
       </c>
       <c r="E3">
-        <v>-419.269</v>
+        <v>-410.138</v>
       </c>
       <c r="F3">
-        <v>9.130999999999998</v>
+        <v>18.262</v>
       </c>
       <c r="G3">
         <v>128.8</v>
@@ -1533,28 +1533,28 @@
         <v>147.1</v>
       </c>
       <c r="M3">
-        <v>0.4592892999999999</v>
+        <v>0.9185785999999998</v>
       </c>
       <c r="N3">
-        <v>146.6407107</v>
+        <v>146.1814214</v>
       </c>
       <c r="O3">
-        <v>39.592991889</v>
+        <v>39.46898377799999</v>
       </c>
       <c r="P3">
-        <v>107.047718811</v>
+        <v>106.712437622</v>
       </c>
       <c r="Q3">
-        <v>134.447718811</v>
+        <v>134.112437622</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.0769370706613394</v>
+        <v>0.0771696379970517</v>
       </c>
       <c r="T3">
-        <v>0.5702863840499809</v>
+        <v>0.5745459364778268</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1571,7 +1571,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>320.2774373363368</v>
+        <v>160.1387186681684</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1579,22 +1579,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.07636062523711068</v>
+        <v>0.07618636051949533</v>
       </c>
       <c r="C4">
-        <v>854.2394672000053</v>
+        <v>847.9281254996065</v>
       </c>
       <c r="D4">
-        <v>743.7014672000053</v>
+        <v>746.5211254996065</v>
       </c>
       <c r="E4">
-        <v>-410.138</v>
+        <v>-401.007</v>
       </c>
       <c r="F4">
-        <v>18.262</v>
+        <v>27.393</v>
       </c>
       <c r="G4">
         <v>128.8</v>
@@ -1615,28 +1615,28 @@
         <v>147.1</v>
       </c>
       <c r="M4">
-        <v>0.9185785999999998</v>
+        <v>1.3778679</v>
       </c>
       <c r="N4">
-        <v>146.1814214</v>
+        <v>145.7221321</v>
       </c>
       <c r="O4">
-        <v>39.46898377799999</v>
+        <v>39.34497566699999</v>
       </c>
       <c r="P4">
-        <v>106.712437622</v>
+        <v>106.377156433</v>
       </c>
       <c r="Q4">
-        <v>134.112437622</v>
+        <v>133.777156433</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.0771696379970517</v>
+        <v>0.07740700053556221</v>
       </c>
       <c r="T4">
-        <v>0.5745459364778268</v>
+        <v>0.5788933147289271</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1653,7 +1653,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>160.1387186681684</v>
+        <v>106.7591457787789</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1661,22 +1661,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.07618636051949533</v>
+        <v>0.07601209580188002</v>
       </c>
       <c r="C5">
-        <v>847.9281254996065</v>
+        <v>841.6382459888058</v>
       </c>
       <c r="D5">
-        <v>746.5211254996065</v>
+        <v>749.3622459888059</v>
       </c>
       <c r="E5">
-        <v>-401.007</v>
+        <v>-391.876</v>
       </c>
       <c r="F5">
-        <v>27.393</v>
+        <v>36.52399999999999</v>
       </c>
       <c r="G5">
         <v>128.8</v>
@@ -1697,28 +1697,28 @@
         <v>147.1</v>
       </c>
       <c r="M5">
-        <v>1.3778679</v>
+        <v>1.8371572</v>
       </c>
       <c r="N5">
-        <v>145.7221321</v>
+        <v>145.2628428</v>
       </c>
       <c r="O5">
-        <v>39.34497566699999</v>
+        <v>39.22096755599999</v>
       </c>
       <c r="P5">
-        <v>106.377156433</v>
+        <v>106.041875244</v>
       </c>
       <c r="Q5">
-        <v>133.777156433</v>
+        <v>133.441875244</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.07740700053556221</v>
+        <v>0.07764930812695836</v>
       </c>
       <c r="T5">
-        <v>0.5788933147289271</v>
+        <v>0.5833312633602589</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1735,7 +1735,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>106.7591457787789</v>
+        <v>80.0693593340842</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1743,22 +1743,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.07601209580188002</v>
+        <v>0.0758378310842647</v>
       </c>
       <c r="C6">
-        <v>841.6382459888058</v>
+        <v>835.3700746470561</v>
       </c>
       <c r="D6">
-        <v>749.3622459888059</v>
+        <v>752.2250746470561</v>
       </c>
       <c r="E6">
-        <v>-391.876</v>
+        <v>-382.745</v>
       </c>
       <c r="F6">
-        <v>36.52399999999999</v>
+        <v>45.655</v>
       </c>
       <c r="G6">
         <v>128.8</v>
@@ -1779,28 +1779,28 @@
         <v>147.1</v>
       </c>
       <c r="M6">
-        <v>1.8371572</v>
+        <v>2.2964465</v>
       </c>
       <c r="N6">
-        <v>145.2628428</v>
+        <v>144.8035535</v>
       </c>
       <c r="O6">
-        <v>39.22096755599999</v>
+        <v>39.096959445</v>
       </c>
       <c r="P6">
-        <v>106.041875244</v>
+        <v>105.706594055</v>
       </c>
       <c r="Q6">
-        <v>133.441875244</v>
+        <v>133.106594055</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.07764930812695836</v>
+        <v>0.07789671693080495</v>
       </c>
       <c r="T6">
-        <v>0.5833312633602589</v>
+        <v>0.5878626424890921</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1817,7 +1817,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>80.0693593340842</v>
+        <v>64.05548746726734</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1825,22 +1825,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.0758378310842647</v>
+        <v>0.07566356636664939</v>
       </c>
       <c r="C7">
-        <v>835.3700746470561</v>
+        <v>829.1238612271375</v>
       </c>
       <c r="D7">
-        <v>752.2250746470561</v>
+        <v>755.1098612271375</v>
       </c>
       <c r="E7">
-        <v>-382.745</v>
+        <v>-373.614</v>
       </c>
       <c r="F7">
-        <v>45.655</v>
+        <v>54.786</v>
       </c>
       <c r="G7">
         <v>128.8</v>
@@ -1861,28 +1861,28 @@
         <v>147.1</v>
       </c>
       <c r="M7">
-        <v>2.2964465</v>
+        <v>2.7557358</v>
       </c>
       <c r="N7">
-        <v>144.8035535</v>
+        <v>144.3442642</v>
       </c>
       <c r="O7">
-        <v>39.096959445</v>
+        <v>38.97295133399999</v>
       </c>
       <c r="P7">
-        <v>105.706594055</v>
+        <v>105.371312866</v>
       </c>
       <c r="Q7">
-        <v>133.106594055</v>
+        <v>132.771312866</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.07789671693080495</v>
+        <v>0.07814938975175467</v>
       </c>
       <c r="T7">
-        <v>0.5878626424890921</v>
+        <v>0.5924904339398157</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1899,7 +1899,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>64.05548746726734</v>
+        <v>53.37957288938946</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1907,22 +1907,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.07566356636664939</v>
+        <v>0.07548930164903407</v>
       </c>
       <c r="C8">
-        <v>829.1238612271376</v>
+        <v>822.899859327793</v>
       </c>
       <c r="D8">
-        <v>755.1098612271375</v>
+        <v>758.0168593277931</v>
       </c>
       <c r="E8">
-        <v>-373.614</v>
+        <v>-364.483</v>
       </c>
       <c r="F8">
-        <v>54.78599999999999</v>
+        <v>63.91699999999999</v>
       </c>
       <c r="G8">
         <v>128.8</v>
@@ -1943,28 +1943,28 @@
         <v>147.1</v>
       </c>
       <c r="M8">
-        <v>2.7557358</v>
+        <v>3.215025099999999</v>
       </c>
       <c r="N8">
-        <v>144.3442642</v>
+        <v>143.8849749</v>
       </c>
       <c r="O8">
-        <v>38.97295133399999</v>
+        <v>38.848943223</v>
       </c>
       <c r="P8">
-        <v>105.371312866</v>
+        <v>105.036031677</v>
       </c>
       <c r="Q8">
-        <v>132.771312866</v>
+        <v>132.436031677</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.07814938975175467</v>
+        <v>0.07840749639681083</v>
       </c>
       <c r="T8">
-        <v>0.5924904339398157</v>
+        <v>0.5972177477873288</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1981,7 +1981,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>53.37957288938946</v>
+        <v>45.75391961947669</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1989,22 +1989,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.07548930164903406</v>
+        <v>0.07531503693141875</v>
       </c>
       <c r="C9">
-        <v>822.8998593277933</v>
+        <v>816.6983264680428</v>
       </c>
       <c r="D9">
-        <v>758.0168593277933</v>
+        <v>760.9463264680428</v>
       </c>
       <c r="E9">
-        <v>-364.4829999999999</v>
+        <v>-355.352</v>
       </c>
       <c r="F9">
-        <v>63.917</v>
+        <v>73.04799999999999</v>
       </c>
       <c r="G9">
         <v>128.8</v>
@@ -2025,28 +2025,28 @@
         <v>147.1</v>
       </c>
       <c r="M9">
-        <v>3.2150251</v>
+        <v>3.674314399999999</v>
       </c>
       <c r="N9">
-        <v>143.8849749</v>
+        <v>143.4256856</v>
       </c>
       <c r="O9">
-        <v>38.848943223</v>
+        <v>38.724935112</v>
       </c>
       <c r="P9">
-        <v>105.036031677</v>
+        <v>104.700750488</v>
       </c>
       <c r="Q9">
-        <v>132.436031677</v>
+        <v>132.100750488</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.07840749639681083</v>
+        <v>0.07867121405588995</v>
       </c>
       <c r="T9">
-        <v>0.5972177477873288</v>
+        <v>0.6020478293271794</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2063,7 +2063,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>45.75391961947668</v>
+        <v>40.03467966704211</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2071,22 +2071,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.07531503693141875</v>
+        <v>0.07514077221380343</v>
       </c>
       <c r="C10">
-        <v>816.6983264680428</v>
+        <v>810.5195241632313</v>
       </c>
       <c r="D10">
-        <v>760.9463264680428</v>
+        <v>763.8985241632313</v>
       </c>
       <c r="E10">
-        <v>-355.352</v>
+        <v>-346.221</v>
       </c>
       <c r="F10">
-        <v>73.04799999999999</v>
+        <v>82.17899999999999</v>
       </c>
       <c r="G10">
         <v>128.8</v>
@@ -2107,28 +2107,28 @@
         <v>147.1</v>
       </c>
       <c r="M10">
-        <v>3.674314399999999</v>
+        <v>4.133603699999999</v>
       </c>
       <c r="N10">
-        <v>143.4256856</v>
+        <v>142.9663963</v>
       </c>
       <c r="O10">
-        <v>38.724935112</v>
+        <v>38.60092700099999</v>
       </c>
       <c r="P10">
-        <v>104.700750488</v>
+        <v>104.365469299</v>
       </c>
       <c r="Q10">
-        <v>132.100750488</v>
+        <v>131.765469299</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.07867121405588995</v>
+        <v>0.07894072770747629</v>
       </c>
       <c r="T10">
-        <v>0.6020478293271794</v>
+        <v>0.6069840665052683</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2145,7 +2145,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>40.03467966704211</v>
+        <v>35.58638192625964</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2153,22 +2153,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.07514077221380343</v>
+        <v>0.07496650749618811</v>
       </c>
       <c r="C11">
-        <v>810.5195241632313</v>
+        <v>804.3637180028504</v>
       </c>
       <c r="D11">
-        <v>763.8985241632313</v>
+        <v>766.8737180028504</v>
       </c>
       <c r="E11">
-        <v>-346.221</v>
+        <v>-337.09</v>
       </c>
       <c r="F11">
-        <v>82.17899999999999</v>
+        <v>91.30999999999999</v>
       </c>
       <c r="G11">
         <v>128.8</v>
@@ -2189,28 +2189,28 @@
         <v>147.1</v>
       </c>
       <c r="M11">
-        <v>4.133603699999999</v>
+        <v>4.592892999999999</v>
       </c>
       <c r="N11">
-        <v>142.9663963</v>
+        <v>142.507107</v>
       </c>
       <c r="O11">
-        <v>38.60092700099999</v>
+        <v>38.47691888999999</v>
       </c>
       <c r="P11">
-        <v>104.365469299</v>
+        <v>104.03018811</v>
       </c>
       <c r="Q11">
-        <v>131.765469299</v>
+        <v>131.43018811</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.07894072770747629</v>
+        <v>0.07921623055132011</v>
       </c>
       <c r="T11">
-        <v>0.6069840665052683</v>
+        <v>0.6120299978428703</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>35.58638192625964</v>
+        <v>32.02774373363368</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2235,22 +2235,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.07496650749618811</v>
+        <v>0.07479224277857277</v>
       </c>
       <c r="C12">
-        <v>804.3637180028504</v>
+        <v>798.2311777301895</v>
       </c>
       <c r="D12">
-        <v>766.8737180028504</v>
+        <v>769.8721777301896</v>
       </c>
       <c r="E12">
-        <v>-337.09</v>
+        <v>-327.959</v>
       </c>
       <c r="F12">
-        <v>91.31</v>
+        <v>100.441</v>
       </c>
       <c r="G12">
         <v>128.8</v>
@@ -2271,28 +2271,28 @@
         <v>147.1</v>
       </c>
       <c r="M12">
-        <v>4.592893</v>
+        <v>5.052182299999999</v>
       </c>
       <c r="N12">
-        <v>142.507107</v>
+        <v>142.0478177</v>
       </c>
       <c r="O12">
-        <v>38.47691888999999</v>
+        <v>38.35291077899999</v>
       </c>
       <c r="P12">
-        <v>104.03018811</v>
+        <v>103.694906921</v>
       </c>
       <c r="Q12">
-        <v>131.43018811</v>
+        <v>131.094906921</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.07921623055132011</v>
+        <v>0.07949792447030649</v>
       </c>
       <c r="T12">
-        <v>0.6120299978428703</v>
+        <v>0.617189320895924</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -2309,7 +2309,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>32.02774373363367</v>
+        <v>29.11613066693971</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2317,22 +2317,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.07479224277857277</v>
+        <v>0.07461797806095746</v>
       </c>
       <c r="C13">
-        <v>798.2311777301895</v>
+        <v>792.1221773238586</v>
       </c>
       <c r="D13">
-        <v>769.8721777301896</v>
+        <v>772.8941773238587</v>
       </c>
       <c r="E13">
-        <v>-327.959</v>
+        <v>-318.828</v>
       </c>
       <c r="F13">
-        <v>100.441</v>
+        <v>109.572</v>
       </c>
       <c r="G13">
         <v>128.8</v>
@@ -2353,28 +2353,28 @@
         <v>147.1</v>
       </c>
       <c r="M13">
-        <v>5.052182299999999</v>
+        <v>5.511471599999999</v>
       </c>
       <c r="N13">
-        <v>142.0478177</v>
+        <v>141.5885284</v>
       </c>
       <c r="O13">
-        <v>38.35291077899999</v>
+        <v>38.228902668</v>
       </c>
       <c r="P13">
-        <v>103.694906921</v>
+        <v>103.359625732</v>
       </c>
       <c r="Q13">
-        <v>131.094906921</v>
+        <v>130.759625732</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.07949792447030649</v>
+        <v>0.0797860205238153</v>
       </c>
       <c r="T13">
-        <v>0.617189320895924</v>
+        <v>0.6224659012910927</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -2391,7 +2391,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>29.11613066693971</v>
+        <v>26.68978644469473</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2399,22 +2399,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.07461797806095746</v>
+        <v>0.07444371334334214</v>
       </c>
       <c r="C14">
-        <v>792.1221773238586</v>
+        <v>786.0369950812437</v>
       </c>
       <c r="D14">
-        <v>772.8941773238587</v>
+        <v>775.9399950812438</v>
       </c>
       <c r="E14">
-        <v>-318.828</v>
+        <v>-309.697</v>
       </c>
       <c r="F14">
-        <v>109.572</v>
+        <v>118.703</v>
       </c>
       <c r="G14">
         <v>128.8</v>
@@ -2435,28 +2435,28 @@
         <v>147.1</v>
       </c>
       <c r="M14">
-        <v>5.511471599999999</v>
+        <v>5.970760899999999</v>
       </c>
       <c r="N14">
-        <v>141.5885284</v>
+        <v>141.1292391</v>
       </c>
       <c r="O14">
-        <v>38.228902668</v>
+        <v>38.10489455699999</v>
       </c>
       <c r="P14">
-        <v>103.359625732</v>
+        <v>103.024344543</v>
       </c>
       <c r="Q14">
-        <v>130.759625732</v>
+        <v>130.424344543</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.0797860205238153</v>
+        <v>0.08008073947510591</v>
       </c>
       <c r="T14">
-        <v>0.6224659012910927</v>
+        <v>0.6278637823850007</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -2473,7 +2473,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>26.68978644469473</v>
+        <v>24.63672594894899</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2481,22 +2481,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.07444371334334214</v>
+        <v>0.07426944862572681</v>
       </c>
       <c r="C15">
-        <v>786.0369950812437</v>
+        <v>779.9759137039382</v>
       </c>
       <c r="D15">
-        <v>775.9399950812438</v>
+        <v>779.0099137039382</v>
       </c>
       <c r="E15">
-        <v>-309.697</v>
+        <v>-300.566</v>
       </c>
       <c r="F15">
-        <v>118.703</v>
+        <v>127.834</v>
       </c>
       <c r="G15">
         <v>128.8</v>
@@ -2517,28 +2517,28 @@
         <v>147.1</v>
       </c>
       <c r="M15">
-        <v>5.970760899999999</v>
+        <v>6.4300502</v>
       </c>
       <c r="N15">
-        <v>141.1292391</v>
+        <v>140.6699498</v>
       </c>
       <c r="O15">
-        <v>38.10489455699999</v>
+        <v>37.98088644599999</v>
       </c>
       <c r="P15">
-        <v>103.024344543</v>
+        <v>102.689063354</v>
       </c>
       <c r="Q15">
-        <v>130.424344543</v>
+        <v>130.089063354</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.08008073947510591</v>
+        <v>0.08038231235549628</v>
       </c>
       <c r="T15">
-        <v>0.6278637823850007</v>
+        <v>0.6333871955973718</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -2555,7 +2555,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>24.63672594894899</v>
+        <v>22.87695980973834</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2563,22 +2563,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.07426944862572681</v>
+        <v>0.0740951839081115</v>
       </c>
       <c r="C16">
-        <v>779.9759137039382</v>
+        <v>773.9392203852129</v>
       </c>
       <c r="D16">
-        <v>779.0099137039382</v>
+        <v>782.1042203852129</v>
       </c>
       <c r="E16">
-        <v>-300.566</v>
+        <v>-291.4349999999999</v>
       </c>
       <c r="F16">
-        <v>127.834</v>
+        <v>136.965</v>
       </c>
       <c r="G16">
         <v>128.8</v>
@@ -2599,28 +2599,28 @@
         <v>147.1</v>
       </c>
       <c r="M16">
-        <v>6.4300502</v>
+        <v>6.8893395</v>
       </c>
       <c r="N16">
-        <v>140.6699498</v>
+        <v>140.2106605</v>
       </c>
       <c r="O16">
-        <v>37.98088644599999</v>
+        <v>37.85687833499999</v>
       </c>
       <c r="P16">
-        <v>102.689063354</v>
+        <v>102.353782165</v>
       </c>
       <c r="Q16">
-        <v>130.089063354</v>
+        <v>129.753782165</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.08038231235549628</v>
+        <v>0.08069098106836647</v>
       </c>
       <c r="T16">
-        <v>0.6333871955973718</v>
+        <v>0.6390405714735635</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -2637,7 +2637,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>22.87695980973834</v>
+        <v>21.35182915575578</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2645,22 +2645,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.0740951839081115</v>
+        <v>0.07392091919049616</v>
       </c>
       <c r="C17">
-        <v>773.939220385213</v>
+        <v>767.9272068995811</v>
       </c>
       <c r="D17">
-        <v>782.1042203852129</v>
+        <v>785.2232068995811</v>
       </c>
       <c r="E17">
-        <v>-291.435</v>
+        <v>-282.304</v>
       </c>
       <c r="F17">
-        <v>136.965</v>
+        <v>146.096</v>
       </c>
       <c r="G17">
         <v>128.8</v>
@@ -2681,28 +2681,28 @@
         <v>147.1</v>
       </c>
       <c r="M17">
-        <v>6.889339499999998</v>
+        <v>7.348628799999998</v>
       </c>
       <c r="N17">
-        <v>140.2106605</v>
+        <v>139.7513712</v>
       </c>
       <c r="O17">
-        <v>37.85687833499999</v>
+        <v>37.732870224</v>
       </c>
       <c r="P17">
-        <v>102.353782165</v>
+        <v>102.018500976</v>
       </c>
       <c r="Q17">
-        <v>129.753782165</v>
+        <v>129.418500976</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.08069098106836647</v>
+        <v>0.08100699903630496</v>
       </c>
       <c r="T17">
-        <v>0.6390405714735635</v>
+        <v>0.6448285515372834</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -2719,7 +2719,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>21.35182915575579</v>
+        <v>20.01733983352105</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2727,22 +2727,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.07392091919049616</v>
+        <v>0.07374665447288085</v>
       </c>
       <c r="C18">
-        <v>767.9272068995811</v>
+        <v>761.9401696945093</v>
       </c>
       <c r="D18">
-        <v>785.2232068995811</v>
+        <v>788.3671696945092</v>
       </c>
       <c r="E18">
-        <v>-282.304</v>
+        <v>-273.173</v>
       </c>
       <c r="F18">
-        <v>146.096</v>
+        <v>155.227</v>
       </c>
       <c r="G18">
         <v>128.8</v>
@@ -2763,28 +2763,28 @@
         <v>147.1</v>
       </c>
       <c r="M18">
-        <v>7.348628799999998</v>
+        <v>7.8079181</v>
       </c>
       <c r="N18">
-        <v>139.7513712</v>
+        <v>139.2920819</v>
       </c>
       <c r="O18">
-        <v>37.732870224</v>
+        <v>37.60886211299999</v>
       </c>
       <c r="P18">
-        <v>102.018500976</v>
+        <v>101.683219787</v>
       </c>
       <c r="Q18">
-        <v>129.418500976</v>
+        <v>129.083219787</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.08100699903630496</v>
+        <v>0.08133063189503717</v>
       </c>
       <c r="T18">
-        <v>0.6448285515372834</v>
+        <v>0.6507560010001292</v>
       </c>
       <c r="U18">
         <v>0.0503</v>
@@ -2801,7 +2801,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>20.01733983352105</v>
+        <v>18.83984925507863</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2809,22 +2809,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.07374665447288085</v>
+        <v>0.07357238975526553</v>
       </c>
       <c r="C19">
-        <v>761.9401696945093</v>
+        <v>755.9784099843473</v>
       </c>
       <c r="D19">
-        <v>788.3671696945092</v>
+        <v>791.5364099843472</v>
       </c>
       <c r="E19">
-        <v>-273.173</v>
+        <v>-264.042</v>
       </c>
       <c r="F19">
-        <v>155.227</v>
+        <v>164.358</v>
       </c>
       <c r="G19">
         <v>128.8</v>
@@ -2845,28 +2845,28 @@
         <v>147.1</v>
       </c>
       <c r="M19">
-        <v>7.8079181</v>
+        <v>8.2672074</v>
       </c>
       <c r="N19">
-        <v>139.2920819</v>
+        <v>138.8327926</v>
       </c>
       <c r="O19">
-        <v>37.60886211299999</v>
+        <v>37.484854002</v>
       </c>
       <c r="P19">
-        <v>101.683219787</v>
+        <v>101.347938598</v>
       </c>
       <c r="Q19">
-        <v>129.083219787</v>
+        <v>128.747938598</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.08133063189503717</v>
+        <v>0.0816621582381287</v>
       </c>
       <c r="T19">
-        <v>0.6507560010001292</v>
+        <v>0.6568280224010931</v>
       </c>
       <c r="U19">
         <v>0.0503</v>
@@ -2883,7 +2883,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>18.83984925507863</v>
+        <v>17.79319096312982</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2891,22 +2891,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.07357238975526555</v>
+        <v>0.07339812503765021</v>
       </c>
       <c r="C20">
-        <v>755.9784099843471</v>
+        <v>750.0422338465269</v>
       </c>
       <c r="D20">
-        <v>791.536409984347</v>
+        <v>794.7312338465269</v>
       </c>
       <c r="E20">
-        <v>-264.042</v>
+        <v>-254.911</v>
       </c>
       <c r="F20">
-        <v>164.358</v>
+        <v>173.489</v>
       </c>
       <c r="G20">
         <v>128.8</v>
@@ -2927,28 +2927,28 @@
         <v>147.1</v>
       </c>
       <c r="M20">
-        <v>8.267207399999998</v>
+        <v>8.726496699999998</v>
       </c>
       <c r="N20">
-        <v>138.8327926</v>
+        <v>138.3735033</v>
       </c>
       <c r="O20">
-        <v>37.484854002</v>
+        <v>37.360845891</v>
       </c>
       <c r="P20">
-        <v>101.347938598</v>
+        <v>101.012657409</v>
       </c>
       <c r="Q20">
-        <v>128.747938598</v>
+        <v>128.412657409</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.0816621582381287</v>
+        <v>0.08200187041685211</v>
       </c>
       <c r="T20">
-        <v>0.6568280224010931</v>
+        <v>0.6630499702564018</v>
       </c>
       <c r="U20">
         <v>0.0503</v>
@@ -2965,7 +2965,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>17.79319096312982</v>
+        <v>16.85670722822825</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2973,22 +2973,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.07339812503765021</v>
+        <v>0.07322386032003489</v>
       </c>
       <c r="C21">
-        <v>750.0422338465269</v>
+        <v>744.1319523201038</v>
       </c>
       <c r="D21">
-        <v>794.7312338465269</v>
+        <v>797.9519523201037</v>
       </c>
       <c r="E21">
-        <v>-254.911</v>
+        <v>-245.78</v>
       </c>
       <c r="F21">
-        <v>173.489</v>
+        <v>182.62</v>
       </c>
       <c r="G21">
         <v>128.8</v>
@@ -3009,28 +3009,28 @@
         <v>147.1</v>
       </c>
       <c r="M21">
-        <v>8.726496699999998</v>
+        <v>9.185786</v>
       </c>
       <c r="N21">
-        <v>138.3735033</v>
+        <v>137.914214</v>
       </c>
       <c r="O21">
-        <v>37.360845891</v>
+        <v>37.23683777999999</v>
       </c>
       <c r="P21">
-        <v>101.012657409</v>
+        <v>100.67737622</v>
       </c>
       <c r="Q21">
-        <v>128.412657409</v>
+        <v>128.07737622</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.08200187041685211</v>
+        <v>0.0823500754000436</v>
       </c>
       <c r="T21">
-        <v>0.6630499702564018</v>
+        <v>0.6694274668080933</v>
       </c>
       <c r="U21">
         <v>0.0503</v>
@@ -3047,7 +3047,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>16.85670722822825</v>
+        <v>16.01387186681684</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3055,22 +3055,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.07322386032003489</v>
+        <v>0.07304959560241957</v>
       </c>
       <c r="C22">
-        <v>744.1319523201038</v>
+        <v>738.247881506702</v>
       </c>
       <c r="D22">
-        <v>797.9519523201037</v>
+        <v>801.198881506702</v>
       </c>
       <c r="E22">
-        <v>-245.78</v>
+        <v>-236.649</v>
       </c>
       <c r="F22">
-        <v>182.62</v>
+        <v>191.751</v>
       </c>
       <c r="G22">
         <v>128.8</v>
@@ -3091,28 +3091,28 @@
         <v>147.1</v>
       </c>
       <c r="M22">
-        <v>9.185786</v>
+        <v>9.6450753</v>
       </c>
       <c r="N22">
-        <v>137.914214</v>
+        <v>137.4549247</v>
       </c>
       <c r="O22">
-        <v>37.23683777999999</v>
+        <v>37.11282966899999</v>
       </c>
       <c r="P22">
-        <v>100.67737622</v>
+        <v>100.342095031</v>
       </c>
       <c r="Q22">
-        <v>128.07737622</v>
+        <v>127.742095031</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.0823500754000436</v>
+        <v>0.08270709569926527</v>
       </c>
       <c r="T22">
-        <v>0.6694274668080933</v>
+        <v>0.6759664189686883</v>
       </c>
       <c r="U22">
         <v>0.0503</v>
@@ -3129,7 +3129,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>16.01387186681684</v>
+        <v>15.25130653982556</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3137,22 +3137,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.07304959560241957</v>
+        <v>0.07287533088480426</v>
       </c>
       <c r="C23">
-        <v>738.247881506702</v>
+        <v>732.3903426739367</v>
       </c>
       <c r="D23">
-        <v>801.198881506702</v>
+        <v>804.4723426739367</v>
       </c>
       <c r="E23">
-        <v>-236.649</v>
+        <v>-227.518</v>
       </c>
       <c r="F23">
-        <v>191.751</v>
+        <v>200.882</v>
       </c>
       <c r="G23">
         <v>128.8</v>
@@ -3173,28 +3173,28 @@
         <v>147.1</v>
       </c>
       <c r="M23">
-        <v>9.645075299999998</v>
+        <v>10.1043646</v>
       </c>
       <c r="N23">
-        <v>137.4549247</v>
+        <v>136.9956354</v>
       </c>
       <c r="O23">
-        <v>37.11282966899999</v>
+        <v>36.98882155799999</v>
       </c>
       <c r="P23">
-        <v>100.342095031</v>
+        <v>100.006813842</v>
       </c>
       <c r="Q23">
-        <v>127.742095031</v>
+        <v>127.406813842</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.08270709569926527</v>
+        <v>0.08307327036513365</v>
       </c>
       <c r="T23">
-        <v>0.6759664189686883</v>
+        <v>0.6826730365692986</v>
       </c>
       <c r="U23">
         <v>0.0503</v>
@@ -3211,7 +3211,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>15.25130653982556</v>
+        <v>14.55806533346985</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3219,22 +3219,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.07287533088480426</v>
+        <v>0.07270106616718892</v>
       </c>
       <c r="C24">
-        <v>732.3903426739367</v>
+        <v>726.5596623613801</v>
       </c>
       <c r="D24">
-        <v>804.4723426739367</v>
+        <v>807.7726623613801</v>
       </c>
       <c r="E24">
-        <v>-227.518</v>
+        <v>-218.387</v>
       </c>
       <c r="F24">
-        <v>200.882</v>
+        <v>210.013</v>
       </c>
       <c r="G24">
         <v>128.8</v>
@@ -3255,28 +3255,28 @@
         <v>147.1</v>
       </c>
       <c r="M24">
-        <v>10.1043646</v>
+        <v>10.5636539</v>
       </c>
       <c r="N24">
-        <v>136.9956354</v>
+        <v>136.5363461</v>
       </c>
       <c r="O24">
-        <v>36.98882155799999</v>
+        <v>36.864813447</v>
       </c>
       <c r="P24">
-        <v>100.006813842</v>
+        <v>99.67153265299999</v>
       </c>
       <c r="Q24">
-        <v>127.406813842</v>
+        <v>127.071532653</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.08307327036513365</v>
+        <v>0.08344895606128432</v>
       </c>
       <c r="T24">
-        <v>0.6826730365692986</v>
+        <v>0.6895538520296649</v>
       </c>
       <c r="U24">
         <v>0.0503</v>
@@ -3293,7 +3293,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>14.55806533346985</v>
+        <v>13.92510597114508</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3301,22 +3301,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.07270106616718892</v>
+        <v>0.07252680144957359</v>
       </c>
       <c r="C25">
-        <v>726.5596623613801</v>
+        <v>720.7561724891452</v>
       </c>
       <c r="D25">
-        <v>807.7726623613801</v>
+        <v>811.1001724891453</v>
       </c>
       <c r="E25">
-        <v>-218.387</v>
+        <v>-209.256</v>
       </c>
       <c r="F25">
-        <v>210.013</v>
+        <v>219.144</v>
       </c>
       <c r="G25">
         <v>128.8</v>
@@ -3337,28 +3337,28 @@
         <v>147.1</v>
       </c>
       <c r="M25">
-        <v>10.5636539</v>
+        <v>11.0229432</v>
       </c>
       <c r="N25">
-        <v>136.5363461</v>
+        <v>136.0770568</v>
       </c>
       <c r="O25">
-        <v>36.864813447</v>
+        <v>36.74080533599999</v>
       </c>
       <c r="P25">
-        <v>99.67153265299999</v>
+        <v>99.33625146399999</v>
       </c>
       <c r="Q25">
-        <v>127.071532653</v>
+        <v>126.736251464</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.08344895606128432</v>
+        <v>0.08383452822312315</v>
       </c>
       <c r="T25">
-        <v>0.6895538520296649</v>
+        <v>0.6966157415810935</v>
       </c>
       <c r="U25">
         <v>0.0503</v>
@@ -3375,7 +3375,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>13.92510597114508</v>
+        <v>13.34489322234736</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3383,22 +3383,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.07252680144957359</v>
+        <v>0.07262628673195828</v>
       </c>
       <c r="C26">
-        <v>720.7561724891452</v>
+        <v>709.7221935893209</v>
       </c>
       <c r="D26">
-        <v>811.1001724891453</v>
+        <v>809.1971935893209</v>
       </c>
       <c r="E26">
-        <v>-209.256</v>
+        <v>-200.125</v>
       </c>
       <c r="F26">
-        <v>219.144</v>
+        <v>228.275</v>
       </c>
       <c r="G26">
         <v>128.8</v>
@@ -3419,45 +3419,45 @@
         <v>147.1</v>
       </c>
       <c r="M26">
-        <v>11.0229432</v>
+        <v>11.824645</v>
       </c>
       <c r="N26">
-        <v>136.0770568</v>
+        <v>135.275355</v>
       </c>
       <c r="O26">
-        <v>36.74080533599999</v>
+        <v>36.52434584999999</v>
       </c>
       <c r="P26">
-        <v>99.33625146399999</v>
+        <v>98.75100914999997</v>
       </c>
       <c r="Q26">
-        <v>126.736251464</v>
+        <v>126.15100915</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.08383452822312315</v>
+        <v>0.08423038230927771</v>
       </c>
       <c r="T26">
-        <v>0.6966157415810935</v>
+        <v>0.703865948187227</v>
       </c>
       <c r="U26">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V26">
         <v>0.27</v>
       </c>
       <c r="W26">
-        <v>0.03671899999999999</v>
+        <v>0.037814</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y26">
-        <v>13.34489322234737</v>
+        <v>12.44011976680907</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3465,22 +3465,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.07262628673195828</v>
+        <v>0.07246297201434296</v>
       </c>
       <c r="C27">
-        <v>709.7221935893209</v>
+        <v>703.719838201695</v>
       </c>
       <c r="D27">
-        <v>809.1971935893209</v>
+        <v>812.325838201695</v>
       </c>
       <c r="E27">
-        <v>-200.125</v>
+        <v>-190.994</v>
       </c>
       <c r="F27">
-        <v>228.275</v>
+        <v>237.406</v>
       </c>
       <c r="G27">
         <v>128.8</v>
@@ -3501,28 +3501,28 @@
         <v>147.1</v>
       </c>
       <c r="M27">
-        <v>11.824645</v>
+        <v>12.2976308</v>
       </c>
       <c r="N27">
-        <v>135.275355</v>
+        <v>134.8023692</v>
       </c>
       <c r="O27">
-        <v>36.52434584999999</v>
+        <v>36.39663968399999</v>
       </c>
       <c r="P27">
-        <v>98.75100914999997</v>
+        <v>98.40572951599997</v>
       </c>
       <c r="Q27">
-        <v>126.15100915</v>
+        <v>125.805729516</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.08423038230927771</v>
+        <v>0.08463693515451751</v>
       </c>
       <c r="T27">
-        <v>0.703865948187227</v>
+        <v>0.7113121063232558</v>
       </c>
       <c r="U27">
         <v>0.0518</v>
@@ -3539,7 +3539,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>12.44011976680907</v>
+        <v>11.96165362193179</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3547,22 +3547,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.07246297201434296</v>
+        <v>0.07229965729672763</v>
       </c>
       <c r="C28">
-        <v>703.719838201695</v>
+        <v>697.7417696247205</v>
       </c>
       <c r="D28">
-        <v>812.325838201695</v>
+        <v>815.4787696247205</v>
       </c>
       <c r="E28">
-        <v>-190.994</v>
+        <v>-181.863</v>
       </c>
       <c r="F28">
-        <v>237.406</v>
+        <v>246.537</v>
       </c>
       <c r="G28">
         <v>128.8</v>
@@ -3583,28 +3583,28 @@
         <v>147.1</v>
       </c>
       <c r="M28">
-        <v>12.2976308</v>
+        <v>12.7706166</v>
       </c>
       <c r="N28">
-        <v>134.8023692</v>
+        <v>134.3293834</v>
       </c>
       <c r="O28">
-        <v>36.39663968399999</v>
+        <v>36.26893351799999</v>
       </c>
       <c r="P28">
-        <v>98.40572951599997</v>
+        <v>98.06044988199997</v>
       </c>
       <c r="Q28">
-        <v>125.805729516</v>
+        <v>125.460449882</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.08463693515451751</v>
+        <v>0.08505462643387347</v>
       </c>
       <c r="T28">
-        <v>0.7113121063232558</v>
+        <v>0.7189622687917788</v>
       </c>
       <c r="U28">
         <v>0.0518</v>
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>11.96165362193179</v>
+        <v>11.5186294137121</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3629,22 +3629,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.07229965729672763</v>
+        <v>0.07213634257911231</v>
       </c>
       <c r="C29">
-        <v>697.7417696247205</v>
+        <v>691.7882717580973</v>
       </c>
       <c r="D29">
-        <v>815.4787696247205</v>
+        <v>818.6562717580973</v>
       </c>
       <c r="E29">
-        <v>-181.863</v>
+        <v>-172.732</v>
       </c>
       <c r="F29">
-        <v>246.537</v>
+        <v>255.668</v>
       </c>
       <c r="G29">
         <v>128.8</v>
@@ -3665,28 +3665,28 @@
         <v>147.1</v>
       </c>
       <c r="M29">
-        <v>12.7706166</v>
+        <v>13.2436024</v>
       </c>
       <c r="N29">
-        <v>134.3293834</v>
+        <v>133.8563976</v>
       </c>
       <c r="O29">
-        <v>36.26893351799999</v>
+        <v>36.14122735199999</v>
       </c>
       <c r="P29">
-        <v>98.06044988199997</v>
+        <v>97.71517024799999</v>
       </c>
       <c r="Q29">
-        <v>125.460449882</v>
+        <v>125.115170248</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.08505462643387347</v>
+        <v>0.0854839202487671</v>
       </c>
       <c r="T29">
-        <v>0.7189622687917788</v>
+        <v>0.7268249357733161</v>
       </c>
       <c r="U29">
         <v>0.0518</v>
@@ -3703,7 +3703,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>11.5186294137121</v>
+        <v>11.10724979179381</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3711,22 +3711,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.07213634257911231</v>
+        <v>0.07197302786149699</v>
       </c>
       <c r="C30">
-        <v>691.7882717580973</v>
+        <v>685.8596329436793</v>
       </c>
       <c r="D30">
-        <v>818.6562717580973</v>
+        <v>821.8586329436794</v>
       </c>
       <c r="E30">
-        <v>-172.732</v>
+        <v>-163.601</v>
       </c>
       <c r="F30">
-        <v>255.668</v>
+        <v>264.799</v>
       </c>
       <c r="G30">
         <v>128.8</v>
@@ -3747,28 +3747,28 @@
         <v>147.1</v>
       </c>
       <c r="M30">
-        <v>13.2436024</v>
+        <v>13.7165882</v>
       </c>
       <c r="N30">
-        <v>133.8563976</v>
+        <v>133.3834118</v>
       </c>
       <c r="O30">
-        <v>36.14122735199999</v>
+        <v>36.013521186</v>
       </c>
       <c r="P30">
-        <v>97.71517024799999</v>
+        <v>97.36989061399998</v>
       </c>
       <c r="Q30">
-        <v>125.115170248</v>
+        <v>124.769890614</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.0854839202487671</v>
+        <v>0.08592530684717886</v>
       </c>
       <c r="T30">
-        <v>0.7268249357733161</v>
+        <v>0.7349090863317982</v>
       </c>
       <c r="U30">
         <v>0.0518</v>
@@ -3785,7 +3785,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>11.10724979179381</v>
+        <v>10.72424117828368</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3793,22 +3793,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.07197302786149698</v>
+        <v>0.07180971314388167</v>
       </c>
       <c r="C31">
-        <v>685.8596329436798</v>
+        <v>679.9561460526996</v>
       </c>
       <c r="D31">
-        <v>821.8586329436797</v>
+        <v>825.0861460526996</v>
       </c>
       <c r="E31">
-        <v>-163.601</v>
+        <v>-154.47</v>
       </c>
       <c r="F31">
-        <v>264.799</v>
+        <v>273.9299999999999</v>
       </c>
       <c r="G31">
         <v>128.8</v>
@@ -3829,28 +3829,28 @@
         <v>147.1</v>
       </c>
       <c r="M31">
-        <v>13.7165882</v>
+        <v>14.189574</v>
       </c>
       <c r="N31">
-        <v>133.3834118</v>
+        <v>132.910426</v>
       </c>
       <c r="O31">
-        <v>36.013521186</v>
+        <v>35.88581502</v>
       </c>
       <c r="P31">
-        <v>97.36989061399998</v>
+        <v>97.02461097999998</v>
       </c>
       <c r="Q31">
-        <v>124.769890614</v>
+        <v>124.42461098</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.08592530684717886</v>
+        <v>0.08637930449125952</v>
       </c>
       <c r="T31">
-        <v>0.7349090863317982</v>
+        <v>0.7432242126205227</v>
       </c>
       <c r="U31">
         <v>0.0518</v>
@@ -3867,7 +3867,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>10.72424117828368</v>
+        <v>10.36676647234089</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3875,22 +3875,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.07180971314388167</v>
+        <v>0.07164639842626636</v>
       </c>
       <c r="C32">
-        <v>679.9561460526996</v>
+        <v>674.078108575055</v>
       </c>
       <c r="D32">
-        <v>825.0861460526996</v>
+        <v>828.3391085750549</v>
       </c>
       <c r="E32">
-        <v>-154.47</v>
+        <v>-145.339</v>
       </c>
       <c r="F32">
-        <v>273.9299999999999</v>
+        <v>283.061</v>
       </c>
       <c r="G32">
         <v>128.8</v>
@@ -3911,28 +3911,28 @@
         <v>147.1</v>
       </c>
       <c r="M32">
-        <v>14.189574</v>
+        <v>14.6625598</v>
       </c>
       <c r="N32">
-        <v>132.910426</v>
+        <v>132.4374402</v>
       </c>
       <c r="O32">
-        <v>35.88581502</v>
+        <v>35.75810885399999</v>
       </c>
       <c r="P32">
-        <v>97.02461097999998</v>
+        <v>96.67933134599997</v>
       </c>
       <c r="Q32">
-        <v>124.42461098</v>
+        <v>124.079331346</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.08637930449125952</v>
+        <v>0.08684646148734254</v>
       </c>
       <c r="T32">
-        <v>0.7432242126205227</v>
+        <v>0.7517803570625435</v>
       </c>
       <c r="U32">
         <v>0.0518</v>
@@ -3949,7 +3949,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>10.36676647234089</v>
+        <v>10.03235465065247</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3957,22 +3957,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.07164639842626636</v>
+        <v>0.07188020370865102</v>
       </c>
       <c r="C33">
-        <v>674.078108575055</v>
+        <v>660.2979695112829</v>
       </c>
       <c r="D33">
-        <v>828.3391085750549</v>
+        <v>823.6899695112828</v>
       </c>
       <c r="E33">
-        <v>-145.339</v>
+        <v>-136.208</v>
       </c>
       <c r="F33">
-        <v>283.061</v>
+        <v>292.192</v>
       </c>
       <c r="G33">
         <v>128.8</v>
@@ -3993,45 +3993,45 @@
         <v>147.1</v>
       </c>
       <c r="M33">
-        <v>14.6625598</v>
+        <v>15.632272</v>
       </c>
       <c r="N33">
-        <v>132.4374402</v>
+        <v>131.467728</v>
       </c>
       <c r="O33">
-        <v>35.75810885399999</v>
+        <v>35.49628655999999</v>
       </c>
       <c r="P33">
-        <v>96.67933134599997</v>
+        <v>95.97144143999998</v>
       </c>
       <c r="Q33">
-        <v>124.079331346</v>
+        <v>123.37144144</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.08684646148734254</v>
+        <v>0.08732735839507504</v>
       </c>
       <c r="T33">
-        <v>0.7517803570625435</v>
+        <v>0.7605881528116826</v>
       </c>
       <c r="U33">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V33">
         <v>0.27</v>
       </c>
       <c r="W33">
-        <v>0.037814</v>
+        <v>0.039055</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>10.03235465065247</v>
+        <v>9.410020501178588</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4039,22 +4039,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.07188020370865102</v>
+        <v>0.07172929899103569</v>
       </c>
       <c r="C34">
-        <v>660.2979695112829</v>
+        <v>654.1616655658237</v>
       </c>
       <c r="D34">
-        <v>823.6899695112828</v>
+        <v>826.6846655658236</v>
       </c>
       <c r="E34">
-        <v>-136.208</v>
+        <v>-127.077</v>
       </c>
       <c r="F34">
-        <v>292.192</v>
+        <v>301.323</v>
       </c>
       <c r="G34">
         <v>128.8</v>
@@ -4075,28 +4075,28 @@
         <v>147.1</v>
       </c>
       <c r="M34">
-        <v>15.632272</v>
+        <v>16.1207805</v>
       </c>
       <c r="N34">
-        <v>131.467728</v>
+        <v>130.9792195</v>
       </c>
       <c r="O34">
-        <v>35.49628655999999</v>
+        <v>35.36438926499999</v>
       </c>
       <c r="P34">
-        <v>95.97144143999998</v>
+        <v>95.61483023499997</v>
       </c>
       <c r="Q34">
-        <v>123.37144144</v>
+        <v>123.014830235</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.08732735839507504</v>
+        <v>0.08782261043438165</v>
       </c>
       <c r="T34">
-        <v>0.7605881528116826</v>
+        <v>0.7696588678369154</v>
       </c>
       <c r="U34">
         <v>0.0535</v>
@@ -4113,7 +4113,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>9.410020501178588</v>
+        <v>9.124868364779235</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4121,22 +4121,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.07172929899103569</v>
+        <v>0.07157839427342037</v>
       </c>
       <c r="C35">
-        <v>654.1616655658237</v>
+        <v>648.0472167589257</v>
       </c>
       <c r="D35">
-        <v>826.6846655658236</v>
+        <v>829.7012167589257</v>
       </c>
       <c r="E35">
-        <v>-127.077</v>
+        <v>-117.946</v>
       </c>
       <c r="F35">
-        <v>301.323</v>
+        <v>310.454</v>
       </c>
       <c r="G35">
         <v>128.8</v>
@@ -4157,28 +4157,28 @@
         <v>147.1</v>
       </c>
       <c r="M35">
-        <v>16.1207805</v>
+        <v>16.609289</v>
       </c>
       <c r="N35">
-        <v>130.9792195</v>
+        <v>130.490711</v>
       </c>
       <c r="O35">
-        <v>35.36438926499999</v>
+        <v>35.23249197</v>
       </c>
       <c r="P35">
-        <v>95.61483023499997</v>
+        <v>95.25821902999998</v>
       </c>
       <c r="Q35">
-        <v>123.014830235</v>
+        <v>122.65821903</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.08782261043438165</v>
+        <v>0.08833287011124299</v>
       </c>
       <c r="T35">
-        <v>0.7696588678369154</v>
+        <v>0.7790044530144279</v>
       </c>
       <c r="U35">
         <v>0.0535</v>
@@ -4195,7 +4195,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>9.124868364779235</v>
+        <v>8.856489883462199</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4203,22 +4203,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.07157839427342037</v>
+        <v>0.07142748955580505</v>
       </c>
       <c r="C36">
-        <v>648.0472167589257</v>
+        <v>641.9548632133155</v>
       </c>
       <c r="D36">
-        <v>829.7012167589257</v>
+        <v>832.7398632133155</v>
       </c>
       <c r="E36">
-        <v>-117.946</v>
+        <v>-108.815</v>
       </c>
       <c r="F36">
-        <v>310.454</v>
+        <v>319.585</v>
       </c>
       <c r="G36">
         <v>128.8</v>
@@ -4239,28 +4239,28 @@
         <v>147.1</v>
       </c>
       <c r="M36">
-        <v>16.609289</v>
+        <v>17.0977975</v>
       </c>
       <c r="N36">
-        <v>130.490711</v>
+        <v>130.0022025</v>
       </c>
       <c r="O36">
-        <v>35.23249197</v>
+        <v>35.10059467499999</v>
       </c>
       <c r="P36">
-        <v>95.25821902999998</v>
+        <v>94.90160782499996</v>
       </c>
       <c r="Q36">
-        <v>122.65821903</v>
+        <v>122.3016078249999</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.08833287011124299</v>
+        <v>0.08885883008585393</v>
       </c>
       <c r="T36">
-        <v>0.7790044530144279</v>
+        <v>0.7886375946589409</v>
       </c>
       <c r="U36">
         <v>0.0535</v>
@@ -4277,7 +4277,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>8.856489883462199</v>
+        <v>8.603447315363278</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4285,22 +4285,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.07142748955580505</v>
+        <v>0.07127658483818973</v>
       </c>
       <c r="C37">
-        <v>641.9548632133155</v>
+        <v>635.8848485822915</v>
       </c>
       <c r="D37">
-        <v>832.7398632133155</v>
+        <v>835.8008485822915</v>
       </c>
       <c r="E37">
-        <v>-108.815</v>
+        <v>-99.68399999999997</v>
       </c>
       <c r="F37">
-        <v>319.585</v>
+        <v>328.716</v>
       </c>
       <c r="G37">
         <v>128.8</v>
@@ -4321,28 +4321,28 @@
         <v>147.1</v>
       </c>
       <c r="M37">
-        <v>17.0977975</v>
+        <v>17.586306</v>
       </c>
       <c r="N37">
-        <v>130.0022025</v>
+        <v>129.513694</v>
       </c>
       <c r="O37">
-        <v>35.10059467499999</v>
+        <v>34.96869737999999</v>
       </c>
       <c r="P37">
-        <v>94.90160782499996</v>
+        <v>94.54499661999998</v>
       </c>
       <c r="Q37">
-        <v>122.3016078249999</v>
+        <v>121.94499662</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.08885883008585393</v>
+        <v>0.08940122630967147</v>
       </c>
       <c r="T37">
-        <v>0.7886375946589409</v>
+        <v>0.7985717719798449</v>
       </c>
       <c r="U37">
         <v>0.0535</v>
@@ -4359,7 +4359,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>8.603447315363278</v>
+        <v>8.364462667714298</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4367,22 +4367,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.07127658483818974</v>
+        <v>0.07112568012057442</v>
       </c>
       <c r="C38">
-        <v>635.8848485822912</v>
+        <v>629.837420114852</v>
       </c>
       <c r="D38">
-        <v>835.8008485822911</v>
+        <v>838.884420114852</v>
       </c>
       <c r="E38">
-        <v>-99.68400000000003</v>
+        <v>-90.553</v>
       </c>
       <c r="F38">
-        <v>328.716</v>
+        <v>337.847</v>
       </c>
       <c r="G38">
         <v>128.8</v>
@@ -4403,28 +4403,28 @@
         <v>147.1</v>
       </c>
       <c r="M38">
-        <v>17.586306</v>
+        <v>18.0748145</v>
       </c>
       <c r="N38">
-        <v>129.513694</v>
+        <v>129.0251855</v>
       </c>
       <c r="O38">
-        <v>34.96869737999999</v>
+        <v>34.83680008499999</v>
       </c>
       <c r="P38">
-        <v>94.54499661999998</v>
+        <v>94.18838541499997</v>
       </c>
       <c r="Q38">
-        <v>121.94499662</v>
+        <v>121.588385415</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.08940122630967147</v>
+        <v>0.08996084146122924</v>
       </c>
       <c r="T38">
-        <v>0.7985717719798449</v>
+        <v>0.8088213200093488</v>
       </c>
       <c r="U38">
         <v>0.0535</v>
@@ -4441,7 +4441,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>8.364462667714299</v>
+        <v>8.138396109127426</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4449,22 +4449,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.07112568012057442</v>
+        <v>0.0709747754029591</v>
       </c>
       <c r="C39">
-        <v>629.837420114852</v>
+        <v>623.8128287222727</v>
       </c>
       <c r="D39">
-        <v>838.884420114852</v>
+        <v>841.9908287222726</v>
       </c>
       <c r="E39">
-        <v>-90.553</v>
+        <v>-81.42200000000003</v>
       </c>
       <c r="F39">
-        <v>337.847</v>
+        <v>346.978</v>
       </c>
       <c r="G39">
         <v>128.8</v>
@@ -4485,28 +4485,28 @@
         <v>147.1</v>
       </c>
       <c r="M39">
-        <v>18.0748145</v>
+        <v>18.563323</v>
       </c>
       <c r="N39">
-        <v>129.0251855</v>
+        <v>128.536677</v>
       </c>
       <c r="O39">
-        <v>34.83680008499999</v>
+        <v>34.70490278999999</v>
       </c>
       <c r="P39">
-        <v>94.18838541499997</v>
+        <v>93.83177420999998</v>
       </c>
       <c r="Q39">
-        <v>121.588385415</v>
+        <v>121.23177421</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.08996084146122924</v>
+        <v>0.09053850871445016</v>
       </c>
       <c r="T39">
-        <v>0.8088213200093488</v>
+        <v>0.8194014986204499</v>
       </c>
       <c r="U39">
         <v>0.0535</v>
@@ -4523,7 +4523,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>8.138396109127426</v>
+        <v>7.924227790466178</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4531,22 +4531,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.0709747754029591</v>
+        <v>0.07082387068534378</v>
       </c>
       <c r="C40">
-        <v>623.8128287222727</v>
+        <v>617.811329046162</v>
       </c>
       <c r="D40">
-        <v>841.9908287222726</v>
+        <v>845.1203290461618</v>
       </c>
       <c r="E40">
-        <v>-81.42200000000003</v>
+        <v>-72.291</v>
       </c>
       <c r="F40">
-        <v>346.978</v>
+        <v>356.109</v>
       </c>
       <c r="G40">
         <v>128.8</v>
@@ -4567,28 +4567,28 @@
         <v>147.1</v>
       </c>
       <c r="M40">
-        <v>18.563323</v>
+        <v>19.0518315</v>
       </c>
       <c r="N40">
-        <v>128.536677</v>
+        <v>128.0481685</v>
       </c>
       <c r="O40">
-        <v>34.70490278999999</v>
+        <v>34.573005495</v>
       </c>
       <c r="P40">
-        <v>93.83177420999998</v>
+        <v>93.47516300499998</v>
       </c>
       <c r="Q40">
-        <v>121.23177421</v>
+        <v>120.875163005</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.09053850871445016</v>
+        <v>0.09113511587761275</v>
       </c>
       <c r="T40">
-        <v>0.8194014986204499</v>
+        <v>0.8303285683335543</v>
       </c>
       <c r="U40">
         <v>0.0535</v>
@@ -4605,7 +4605,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>7.924227790466178</v>
+        <v>7.721042462505507</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4613,22 +4613,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.07082387068534378</v>
+        <v>0.07090656596772846</v>
       </c>
       <c r="C41">
-        <v>617.811329046162</v>
+        <v>606.9624980279727</v>
       </c>
       <c r="D41">
-        <v>845.1203290461618</v>
+        <v>843.4024980279728</v>
       </c>
       <c r="E41">
-        <v>-72.291</v>
+        <v>-63.15999999999997</v>
       </c>
       <c r="F41">
-        <v>356.109</v>
+        <v>365.24</v>
       </c>
       <c r="G41">
         <v>128.8</v>
@@ -4649,45 +4649,45 @@
         <v>147.1</v>
       </c>
       <c r="M41">
-        <v>19.0518315</v>
+        <v>19.832532</v>
       </c>
       <c r="N41">
-        <v>128.0481685</v>
+        <v>127.267468</v>
       </c>
       <c r="O41">
-        <v>34.573005495</v>
+        <v>34.36221635999999</v>
       </c>
       <c r="P41">
-        <v>93.47516300499998</v>
+        <v>92.90525163999997</v>
       </c>
       <c r="Q41">
-        <v>120.875163005</v>
+        <v>120.30525164</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.09113511587761275</v>
+        <v>0.09175160994621409</v>
       </c>
       <c r="T41">
-        <v>0.8303285683335543</v>
+        <v>0.8416198737037621</v>
       </c>
       <c r="U41">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V41">
         <v>0.27</v>
       </c>
       <c r="W41">
-        <v>0.039055</v>
+        <v>0.039639</v>
       </c>
       <c r="X41" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y41">
-        <v>7.721042462505507</v>
+        <v>7.417106398719032</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4695,22 +4695,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.07090656596772846</v>
+        <v>0.07076150125011313</v>
       </c>
       <c r="C42">
-        <v>606.9624980279727</v>
+        <v>600.8495670089723</v>
       </c>
       <c r="D42">
-        <v>843.4024980279728</v>
+        <v>846.4205670089723</v>
       </c>
       <c r="E42">
-        <v>-63.15999999999997</v>
+        <v>-54.029</v>
       </c>
       <c r="F42">
-        <v>365.24</v>
+        <v>374.371</v>
       </c>
       <c r="G42">
         <v>128.8</v>
@@ -4731,28 +4731,28 @@
         <v>147.1</v>
       </c>
       <c r="M42">
-        <v>19.832532</v>
+        <v>20.3283453</v>
       </c>
       <c r="N42">
-        <v>127.267468</v>
+        <v>126.7716547</v>
       </c>
       <c r="O42">
-        <v>34.36221635999999</v>
+        <v>34.22834676899999</v>
       </c>
       <c r="P42">
-        <v>92.90525163999997</v>
+        <v>92.54330793099999</v>
       </c>
       <c r="Q42">
-        <v>120.30525164</v>
+        <v>119.943307931</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.09175160994621409</v>
+        <v>0.09238900211883583</v>
       </c>
       <c r="T42">
-        <v>0.8416198737037621</v>
+        <v>0.8532939351882142</v>
       </c>
       <c r="U42">
         <v>0.0543</v>
@@ -4769,7 +4769,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>7.417106398719032</v>
+        <v>7.236201364603935</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4777,22 +4777,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.07076150125011313</v>
+        <v>0.07061643653249781</v>
       </c>
       <c r="C43">
-        <v>600.8495670089723</v>
+        <v>594.7583135462405</v>
       </c>
       <c r="D43">
-        <v>846.4205670089723</v>
+        <v>849.4603135462404</v>
       </c>
       <c r="E43">
-        <v>-54.029</v>
+        <v>-44.89799999999997</v>
       </c>
       <c r="F43">
-        <v>374.371</v>
+        <v>383.502</v>
       </c>
       <c r="G43">
         <v>128.8</v>
@@ -4813,28 +4813,28 @@
         <v>147.1</v>
       </c>
       <c r="M43">
-        <v>20.3283453</v>
+        <v>20.8241586</v>
       </c>
       <c r="N43">
-        <v>126.7716547</v>
+        <v>126.2758414</v>
       </c>
       <c r="O43">
-        <v>34.22834676899999</v>
+        <v>34.09447717799999</v>
       </c>
       <c r="P43">
-        <v>92.54330793099999</v>
+        <v>92.18136422199997</v>
       </c>
       <c r="Q43">
-        <v>119.943307931</v>
+        <v>119.581364222</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.09238900211883583</v>
+        <v>0.09304837333189278</v>
       </c>
       <c r="T43">
-        <v>0.8532939351882142</v>
+        <v>0.8653705505169579</v>
       </c>
       <c r="U43">
         <v>0.0543</v>
@@ -4851,7 +4851,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>7.236201364603935</v>
+        <v>7.063910855922887</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4859,22 +4859,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.07061643653249781</v>
+        <v>0.0704713718148825</v>
       </c>
       <c r="C44">
-        <v>594.7583135462405</v>
+        <v>588.6889720330964</v>
       </c>
       <c r="D44">
-        <v>849.4603135462404</v>
+        <v>852.5219720330964</v>
       </c>
       <c r="E44">
-        <v>-44.89800000000002</v>
+        <v>-35.767</v>
       </c>
       <c r="F44">
-        <v>383.502</v>
+        <v>392.633</v>
       </c>
       <c r="G44">
         <v>128.8</v>
@@ -4895,28 +4895,28 @@
         <v>147.1</v>
       </c>
       <c r="M44">
-        <v>20.8241586</v>
+        <v>21.3199719</v>
       </c>
       <c r="N44">
-        <v>126.2758414</v>
+        <v>125.7800281</v>
       </c>
       <c r="O44">
-        <v>34.09447717799999</v>
+        <v>33.96060758699999</v>
       </c>
       <c r="P44">
-        <v>92.18136422199997</v>
+        <v>91.81942051299998</v>
       </c>
       <c r="Q44">
-        <v>119.581364222</v>
+        <v>119.219420513</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.09304837333189277</v>
+        <v>0.09373088037698682</v>
       </c>
       <c r="T44">
-        <v>0.8653705505169575</v>
+        <v>0.8778709067344291</v>
       </c>
       <c r="U44">
         <v>0.0543</v>
@@ -4933,7 +4933,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>7.063910855922889</v>
+        <v>6.899633859273519</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4941,22 +4941,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.0704713718148825</v>
+        <v>0.07032630709726717</v>
       </c>
       <c r="C45">
-        <v>588.6889720330964</v>
+        <v>582.6417802543224</v>
       </c>
       <c r="D45">
-        <v>852.5219720330964</v>
+        <v>855.6057802543223</v>
       </c>
       <c r="E45">
-        <v>-35.767</v>
+        <v>-26.63600000000002</v>
       </c>
       <c r="F45">
-        <v>392.633</v>
+        <v>401.764</v>
       </c>
       <c r="G45">
         <v>128.8</v>
@@ -4977,28 +4977,28 @@
         <v>147.1</v>
       </c>
       <c r="M45">
-        <v>21.3199719</v>
+        <v>21.8157852</v>
       </c>
       <c r="N45">
-        <v>125.7800281</v>
+        <v>125.2842148</v>
       </c>
       <c r="O45">
-        <v>33.96060758699999</v>
+        <v>33.82673799599999</v>
       </c>
       <c r="P45">
-        <v>91.81942051299998</v>
+        <v>91.45747680399998</v>
       </c>
       <c r="Q45">
-        <v>119.219420513</v>
+        <v>118.857476804</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.09373088037698682</v>
+        <v>0.09443776267369136</v>
       </c>
       <c r="T45">
-        <v>0.8778709067344291</v>
+        <v>0.8908177042453815</v>
       </c>
       <c r="U45">
         <v>0.0543</v>
@@ -5015,7 +5015,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>6.899633859273519</v>
+        <v>6.742823998835485</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5023,22 +5023,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.07032630709726717</v>
+        <v>0.07018124237965184</v>
       </c>
       <c r="C46">
-        <v>582.6417802543224</v>
+        <v>576.6169794477237</v>
       </c>
       <c r="D46">
-        <v>855.6057802543223</v>
+        <v>858.7119794477236</v>
       </c>
       <c r="E46">
-        <v>-26.63600000000002</v>
+        <v>-17.505</v>
       </c>
       <c r="F46">
-        <v>401.764</v>
+        <v>410.895</v>
       </c>
       <c r="G46">
         <v>128.8</v>
@@ -5059,28 +5059,28 @@
         <v>147.1</v>
       </c>
       <c r="M46">
-        <v>21.8157852</v>
+        <v>22.3115985</v>
       </c>
       <c r="N46">
-        <v>125.2842148</v>
+        <v>124.7884015</v>
       </c>
       <c r="O46">
-        <v>33.82673799599999</v>
+        <v>33.69286840499999</v>
       </c>
       <c r="P46">
-        <v>91.45747680399998</v>
+        <v>91.09553309499998</v>
       </c>
       <c r="Q46">
-        <v>118.857476804</v>
+        <v>118.495533095</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.09443776267369136</v>
+        <v>0.09517034978118517</v>
       </c>
       <c r="T46">
-        <v>0.8908177042453815</v>
+        <v>0.904235294393096</v>
       </c>
       <c r="U46">
         <v>0.0543</v>
@@ -5097,7 +5097,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>6.742823998835485</v>
+        <v>6.592983465528029</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5105,22 +5105,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.07018124237965184</v>
+        <v>0.07003617766203653</v>
       </c>
       <c r="C47">
-        <v>576.6169794477237</v>
+        <v>570.6148143670379</v>
       </c>
       <c r="D47">
-        <v>858.7119794477236</v>
+        <v>861.8408143670379</v>
       </c>
       <c r="E47">
-        <v>-17.505</v>
+        <v>-8.374000000000024</v>
       </c>
       <c r="F47">
-        <v>410.895</v>
+        <v>420.026</v>
       </c>
       <c r="G47">
         <v>128.8</v>
@@ -5141,28 +5141,28 @@
         <v>147.1</v>
       </c>
       <c r="M47">
-        <v>22.3115985</v>
+        <v>22.8074118</v>
       </c>
       <c r="N47">
-        <v>124.7884015</v>
+        <v>124.2925882</v>
       </c>
       <c r="O47">
-        <v>33.69286840499999</v>
+        <v>33.55899881399999</v>
       </c>
       <c r="P47">
-        <v>91.09553309499998</v>
+        <v>90.73358938599998</v>
       </c>
       <c r="Q47">
-        <v>118.495533095</v>
+        <v>118.133589386</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.09517034978118517</v>
+        <v>0.09593006974451208</v>
       </c>
       <c r="T47">
-        <v>0.904235294393096</v>
+        <v>0.9181498323240592</v>
       </c>
       <c r="U47">
         <v>0.0543</v>
@@ -5179,7 +5179,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>6.592983465528029</v>
+        <v>6.44965773801655</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5187,22 +5187,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.07003617766203653</v>
+        <v>0.06989111294442121</v>
       </c>
       <c r="C48">
-        <v>570.6148143670379</v>
+        <v>564.6355333462241</v>
       </c>
       <c r="D48">
-        <v>861.8408143670379</v>
+        <v>864.9925333462239</v>
       </c>
       <c r="E48">
-        <v>-8.374000000000024</v>
+        <v>0.757000000000005</v>
       </c>
       <c r="F48">
-        <v>420.026</v>
+        <v>429.157</v>
       </c>
       <c r="G48">
         <v>128.8</v>
@@ -5223,28 +5223,28 @@
         <v>147.1</v>
       </c>
       <c r="M48">
-        <v>22.8074118</v>
+        <v>23.3032251</v>
       </c>
       <c r="N48">
-        <v>124.2925882</v>
+        <v>123.7967749</v>
       </c>
       <c r="O48">
-        <v>33.55899881399999</v>
+        <v>33.42512922299999</v>
       </c>
       <c r="P48">
-        <v>90.73358938599998</v>
+        <v>90.37164567699998</v>
       </c>
       <c r="Q48">
-        <v>118.133589386</v>
+        <v>117.771645677</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.09593006974451208</v>
+        <v>0.09671845838570038</v>
       </c>
       <c r="T48">
-        <v>0.9181498323240592</v>
+        <v>0.9325894471580776</v>
       </c>
       <c r="U48">
         <v>0.0543</v>
@@ -5261,7 +5261,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>6.44965773801655</v>
+        <v>6.31243097763322</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5269,22 +5269,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.06989111294442121</v>
+        <v>0.06974604822680588</v>
       </c>
       <c r="C49">
-        <v>564.6355333462241</v>
+        <v>558.6793883651649</v>
       </c>
       <c r="D49">
-        <v>864.9925333462239</v>
+        <v>868.1673883651648</v>
       </c>
       <c r="E49">
-        <v>0.757000000000005</v>
+        <v>9.888000000000034</v>
       </c>
       <c r="F49">
-        <v>429.157</v>
+        <v>438.288</v>
       </c>
       <c r="G49">
         <v>128.8</v>
@@ -5305,28 +5305,28 @@
         <v>147.1</v>
       </c>
       <c r="M49">
-        <v>23.3032251</v>
+        <v>23.7990384</v>
       </c>
       <c r="N49">
-        <v>123.7967749</v>
+        <v>123.3009616</v>
       </c>
       <c r="O49">
-        <v>33.42512922299999</v>
+        <v>33.29125963199999</v>
       </c>
       <c r="P49">
-        <v>90.37164567699998</v>
+        <v>90.00970196799997</v>
       </c>
       <c r="Q49">
-        <v>117.771645677</v>
+        <v>117.409701968</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.09671845838570038</v>
+        <v>0.09753716966693439</v>
       </c>
       <c r="T49">
-        <v>0.9325894471580776</v>
+        <v>0.9475844317934043</v>
       </c>
       <c r="U49">
         <v>0.0543</v>
@@ -5343,7 +5343,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>6.31243097763322</v>
+        <v>6.180921998932527</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5351,22 +5351,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.06974604822680588</v>
+        <v>0.06995868350919056</v>
       </c>
       <c r="C50">
-        <v>558.6793883651649</v>
+        <v>544.9026121941115</v>
       </c>
       <c r="D50">
-        <v>868.1673883651648</v>
+        <v>863.5216121941113</v>
       </c>
       <c r="E50">
-        <v>9.887999999999977</v>
+        <v>19.01899999999995</v>
       </c>
       <c r="F50">
-        <v>438.288</v>
+        <v>447.4189999999999</v>
       </c>
       <c r="G50">
         <v>128.8</v>
@@ -5387,45 +5387,45 @@
         <v>147.1</v>
       </c>
       <c r="M50">
-        <v>23.7990384</v>
+        <v>24.7422707</v>
       </c>
       <c r="N50">
-        <v>123.3009616</v>
+        <v>122.3577293</v>
       </c>
       <c r="O50">
-        <v>33.29125963199999</v>
+        <v>33.03658691099999</v>
       </c>
       <c r="P50">
-        <v>90.00970196799997</v>
+        <v>89.32114238899999</v>
       </c>
       <c r="Q50">
-        <v>117.409701968</v>
+        <v>116.721142389</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.09753716966693439</v>
+        <v>0.09838798727292267</v>
       </c>
       <c r="T50">
-        <v>0.9475844317934043</v>
+        <v>0.9631674550418811</v>
       </c>
       <c r="U50">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V50">
         <v>0.27</v>
       </c>
       <c r="W50">
-        <v>0.039639</v>
+        <v>0.040369</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y50">
-        <v>6.180921998932527</v>
+        <v>5.945291027795601</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5433,22 +5433,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.06995868350919056</v>
+        <v>0.06982091879157523</v>
       </c>
       <c r="C51">
-        <v>544.9026121941115</v>
+        <v>538.7758826814643</v>
       </c>
       <c r="D51">
-        <v>863.5216121941113</v>
+        <v>866.5258826814643</v>
       </c>
       <c r="E51">
-        <v>19.01899999999995</v>
+        <v>28.14999999999998</v>
       </c>
       <c r="F51">
-        <v>447.4189999999999</v>
+        <v>456.55</v>
       </c>
       <c r="G51">
         <v>128.8</v>
@@ -5469,28 +5469,28 @@
         <v>147.1</v>
       </c>
       <c r="M51">
-        <v>24.7422707</v>
+        <v>25.247215</v>
       </c>
       <c r="N51">
-        <v>122.3577293</v>
+        <v>121.852785</v>
       </c>
       <c r="O51">
-        <v>33.03658691099999</v>
+        <v>32.90025194999999</v>
       </c>
       <c r="P51">
-        <v>89.32114238899999</v>
+        <v>88.95253304999997</v>
       </c>
       <c r="Q51">
-        <v>116.721142389</v>
+        <v>116.35253305</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.09838798727292267</v>
+        <v>0.09927283758315048</v>
       </c>
       <c r="T51">
-        <v>0.9631674550418811</v>
+        <v>0.979373799220297</v>
       </c>
       <c r="U51">
         <v>0.0553</v>
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>5.945291027795601</v>
+        <v>5.826385207239689</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5515,22 +5515,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.06982091879157523</v>
+        <v>0.06968315407395992</v>
       </c>
       <c r="C52">
-        <v>538.7758826814643</v>
+        <v>532.6701304129087</v>
       </c>
       <c r="D52">
-        <v>866.5258826814643</v>
+        <v>869.5511304129088</v>
       </c>
       <c r="E52">
-        <v>28.14999999999998</v>
+        <v>37.28100000000001</v>
       </c>
       <c r="F52">
-        <v>456.55</v>
+        <v>465.681</v>
       </c>
       <c r="G52">
         <v>128.8</v>
@@ -5551,28 +5551,28 @@
         <v>147.1</v>
       </c>
       <c r="M52">
-        <v>25.247215</v>
+        <v>25.7521593</v>
       </c>
       <c r="N52">
-        <v>121.852785</v>
+        <v>121.3478407</v>
       </c>
       <c r="O52">
-        <v>32.90025194999999</v>
+        <v>32.76391698899999</v>
       </c>
       <c r="P52">
-        <v>88.95253304999997</v>
+        <v>88.58392371099997</v>
       </c>
       <c r="Q52">
-        <v>116.35253305</v>
+        <v>115.983923711</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.09927283758315048</v>
+        <v>0.1001938042325713</v>
       </c>
       <c r="T52">
-        <v>0.979373799220297</v>
+        <v>0.9962416268345667</v>
       </c>
       <c r="U52">
         <v>0.0553</v>
@@ -5589,7 +5589,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>5.826385207239689</v>
+        <v>5.71214236003891</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5597,22 +5597,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.06968315407395992</v>
+        <v>0.06954538935634459</v>
       </c>
       <c r="C53">
-        <v>532.6701304129087</v>
+        <v>526.5855758678208</v>
       </c>
       <c r="D53">
-        <v>869.5511304129088</v>
+        <v>872.5975758678208</v>
       </c>
       <c r="E53">
-        <v>37.28100000000001</v>
+        <v>46.41199999999998</v>
       </c>
       <c r="F53">
-        <v>465.681</v>
+        <v>474.812</v>
       </c>
       <c r="G53">
         <v>128.8</v>
@@ -5633,28 +5633,28 @@
         <v>147.1</v>
       </c>
       <c r="M53">
-        <v>25.7521593</v>
+        <v>26.2571036</v>
       </c>
       <c r="N53">
-        <v>121.3478407</v>
+        <v>120.8428964</v>
       </c>
       <c r="O53">
-        <v>32.76391698899999</v>
+        <v>32.62758202799999</v>
       </c>
       <c r="P53">
-        <v>88.58392371099997</v>
+        <v>88.21531437199998</v>
       </c>
       <c r="Q53">
-        <v>115.983923711</v>
+        <v>115.615314372</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1001938042325713</v>
+        <v>0.1011531444923846</v>
       </c>
       <c r="T53">
-        <v>0.9962416268345667</v>
+        <v>1.013812280599431</v>
       </c>
       <c r="U53">
         <v>0.0553</v>
@@ -5671,7 +5671,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>5.71214236003891</v>
+        <v>5.602293468499701</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5679,22 +5679,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.06954538935634459</v>
+        <v>0.06940762463872928</v>
       </c>
       <c r="C54">
-        <v>526.5855758678208</v>
+        <v>520.522442626208</v>
       </c>
       <c r="D54">
-        <v>872.5975758678208</v>
+        <v>875.6654426262079</v>
       </c>
       <c r="E54">
-        <v>46.41199999999998</v>
+        <v>55.54300000000001</v>
       </c>
       <c r="F54">
-        <v>474.812</v>
+        <v>483.943</v>
       </c>
       <c r="G54">
         <v>128.8</v>
@@ -5715,28 +5715,28 @@
         <v>147.1</v>
       </c>
       <c r="M54">
-        <v>26.2571036</v>
+        <v>26.7620479</v>
       </c>
       <c r="N54">
-        <v>120.8428964</v>
+        <v>120.3379521</v>
       </c>
       <c r="O54">
-        <v>32.62758202799999</v>
+        <v>32.491247067</v>
       </c>
       <c r="P54">
-        <v>88.21531437199998</v>
+        <v>87.84670503299998</v>
       </c>
       <c r="Q54">
-        <v>115.615314372</v>
+        <v>115.246705033</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1011531444923846</v>
+        <v>0.1021533077419772</v>
       </c>
       <c r="T54">
-        <v>1.013812280599431</v>
+        <v>1.032130621758545</v>
       </c>
       <c r="U54">
         <v>0.0553</v>
@@ -5753,7 +5753,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>5.602293468499701</v>
+        <v>5.49658981815065</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5761,22 +5761,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.06940762463872928</v>
+        <v>0.06926985992111395</v>
       </c>
       <c r="C55">
-        <v>520.522442626208</v>
+        <v>514.4809574234113</v>
       </c>
       <c r="D55">
-        <v>875.6654426262079</v>
+        <v>878.7549574234113</v>
       </c>
       <c r="E55">
-        <v>55.54300000000001</v>
+        <v>64.67399999999998</v>
       </c>
       <c r="F55">
-        <v>483.943</v>
+        <v>493.074</v>
       </c>
       <c r="G55">
         <v>128.8</v>
@@ -5797,28 +5797,28 @@
         <v>147.1</v>
       </c>
       <c r="M55">
-        <v>26.7620479</v>
+        <v>27.2669922</v>
       </c>
       <c r="N55">
-        <v>120.3379521</v>
+        <v>119.8330078</v>
       </c>
       <c r="O55">
-        <v>32.491247067</v>
+        <v>32.35491210599999</v>
       </c>
       <c r="P55">
-        <v>87.84670503299998</v>
+        <v>87.47809569399996</v>
       </c>
       <c r="Q55">
-        <v>115.246705033</v>
+        <v>114.878095694</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1021533077419772</v>
+        <v>0.1031969563502477</v>
       </c>
       <c r="T55">
-        <v>1.032130621758545</v>
+        <v>1.051245412533272</v>
       </c>
       <c r="U55">
         <v>0.0553</v>
@@ -5835,7 +5835,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>5.49658981815065</v>
+        <v>5.394801117814526</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5843,22 +5843,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.06926985992111395</v>
+        <v>0.06913209520349864</v>
       </c>
       <c r="C56">
-        <v>514.4809574234113</v>
+        <v>508.4613502059628</v>
       </c>
       <c r="D56">
-        <v>878.7549574234113</v>
+        <v>881.8663502059628</v>
       </c>
       <c r="E56">
-        <v>64.67399999999998</v>
+        <v>73.80500000000001</v>
       </c>
       <c r="F56">
-        <v>493.074</v>
+        <v>502.205</v>
       </c>
       <c r="G56">
         <v>128.8</v>
@@ -5879,28 +5879,28 @@
         <v>147.1</v>
       </c>
       <c r="M56">
-        <v>27.2669922</v>
+        <v>27.7719365</v>
       </c>
       <c r="N56">
-        <v>119.8330078</v>
+        <v>119.3280635</v>
       </c>
       <c r="O56">
-        <v>32.35491210599999</v>
+        <v>32.218577145</v>
       </c>
       <c r="P56">
-        <v>87.47809569399996</v>
+        <v>87.10948635499997</v>
       </c>
       <c r="Q56">
-        <v>114.878095694</v>
+        <v>114.509486355</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1031969563502477</v>
+        <v>0.1042869893411081</v>
       </c>
       <c r="T56">
-        <v>1.051245412533272</v>
+        <v>1.071209749564654</v>
       </c>
       <c r="U56">
         <v>0.0553</v>
@@ -5917,7 +5917,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>5.394801117814526</v>
+        <v>5.296713824763353</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5925,22 +5925,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.06913209520349864</v>
+        <v>0.06899433048588333</v>
       </c>
       <c r="C57">
-        <v>508.4613502059628</v>
+        <v>502.4638541886377</v>
       </c>
       <c r="D57">
-        <v>881.8663502059628</v>
+        <v>884.9998541886376</v>
       </c>
       <c r="E57">
-        <v>73.80500000000001</v>
+        <v>82.93600000000004</v>
       </c>
       <c r="F57">
-        <v>502.205</v>
+        <v>511.336</v>
       </c>
       <c r="G57">
         <v>128.8</v>
@@ -5961,28 +5961,28 @@
         <v>147.1</v>
       </c>
       <c r="M57">
-        <v>27.7719365</v>
+        <v>28.2768808</v>
       </c>
       <c r="N57">
-        <v>119.3280635</v>
+        <v>118.8231192</v>
       </c>
       <c r="O57">
-        <v>32.218577145</v>
+        <v>32.08224218399999</v>
       </c>
       <c r="P57">
-        <v>87.10948635499997</v>
+        <v>86.74087701599997</v>
       </c>
       <c r="Q57">
-        <v>114.509486355</v>
+        <v>114.140877016</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1042869893411081</v>
+        <v>0.1054265692860984</v>
       </c>
       <c r="T57">
-        <v>1.071209749564654</v>
+        <v>1.092081556461099</v>
       </c>
       <c r="U57">
         <v>0.0553</v>
@@ -5999,7 +5999,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>5.296713824763353</v>
+        <v>5.20212964932115</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6007,22 +6007,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.06899433048588333</v>
+        <v>0.06885656576826799</v>
       </c>
       <c r="C58">
-        <v>502.4638541886377</v>
+        <v>496.4887059127267</v>
       </c>
       <c r="D58">
-        <v>884.9998541886376</v>
+        <v>888.1557059127266</v>
       </c>
       <c r="E58">
-        <v>82.93600000000004</v>
+        <v>92.06700000000001</v>
       </c>
       <c r="F58">
-        <v>511.336</v>
+        <v>520.467</v>
       </c>
       <c r="G58">
         <v>128.8</v>
@@ -6043,28 +6043,28 @@
         <v>147.1</v>
       </c>
       <c r="M58">
-        <v>28.2768808</v>
+        <v>28.7818251</v>
       </c>
       <c r="N58">
-        <v>118.8231192</v>
+        <v>118.3181749</v>
       </c>
       <c r="O58">
-        <v>32.08224218399999</v>
+        <v>31.945907223</v>
       </c>
       <c r="P58">
-        <v>86.74087701599997</v>
+        <v>86.37226767699998</v>
       </c>
       <c r="Q58">
-        <v>114.140877016</v>
+        <v>113.772267677</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1054265692860984</v>
+        <v>0.1066191529494604</v>
       </c>
       <c r="T58">
-        <v>1.092081556461099</v>
+        <v>1.113924145073657</v>
       </c>
       <c r="U58">
         <v>0.0553</v>
@@ -6081,7 +6081,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>5.20212964932115</v>
+        <v>5.11086421687692</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6089,22 +6089,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.06885656576826799</v>
+        <v>0.06871880105065267</v>
       </c>
       <c r="C59">
-        <v>496.4887059127267</v>
+        <v>490.5361453055559</v>
       </c>
       <c r="D59">
-        <v>888.1557059127266</v>
+        <v>891.3341453055558</v>
       </c>
       <c r="E59">
-        <v>92.06700000000001</v>
+        <v>101.198</v>
       </c>
       <c r="F59">
-        <v>520.467</v>
+        <v>529.598</v>
       </c>
       <c r="G59">
         <v>128.8</v>
@@ -6125,28 +6125,28 @@
         <v>147.1</v>
       </c>
       <c r="M59">
-        <v>28.7818251</v>
+        <v>29.2867694</v>
       </c>
       <c r="N59">
-        <v>118.3181749</v>
+        <v>117.8132306</v>
       </c>
       <c r="O59">
-        <v>31.945907223</v>
+        <v>31.80957226199999</v>
       </c>
       <c r="P59">
-        <v>86.37226767699998</v>
+        <v>86.00365833799998</v>
       </c>
       <c r="Q59">
-        <v>113.772267677</v>
+        <v>113.403658338</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1066191529494604</v>
+        <v>0.1078685263110778</v>
       </c>
       <c r="T59">
-        <v>1.113924145073657</v>
+        <v>1.13680685695348</v>
       </c>
       <c r="U59">
         <v>0.0553</v>
@@ -6163,7 +6163,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>5.11086421687692</v>
+        <v>5.022745868310077</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6171,22 +6171,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.06871880105065267</v>
+        <v>0.06858103633303735</v>
       </c>
       <c r="C60">
-        <v>490.5361453055559</v>
+        <v>484.6064157412974</v>
       </c>
       <c r="D60">
-        <v>891.3341453055558</v>
+        <v>894.5354157412972</v>
       </c>
       <c r="E60">
-        <v>101.198</v>
+        <v>110.329</v>
       </c>
       <c r="F60">
-        <v>529.598</v>
+        <v>538.7289999999999</v>
       </c>
       <c r="G60">
         <v>128.8</v>
@@ -6207,28 +6207,28 @@
         <v>147.1</v>
       </c>
       <c r="M60">
-        <v>29.2867694</v>
+        <v>29.7917137</v>
       </c>
       <c r="N60">
-        <v>117.8132306</v>
+        <v>117.3082863</v>
       </c>
       <c r="O60">
-        <v>31.80957226199999</v>
+        <v>31.67323730099999</v>
       </c>
       <c r="P60">
-        <v>86.00365833799998</v>
+        <v>85.63504899899996</v>
       </c>
       <c r="Q60">
-        <v>113.403658338</v>
+        <v>113.035048999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1078685263110778</v>
+        <v>0.1091788447147252</v>
       </c>
       <c r="T60">
-        <v>1.13680685695348</v>
+        <v>1.160805798681099</v>
       </c>
       <c r="U60">
         <v>0.0553</v>
@@ -6245,7 +6245,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>5.022745868310077</v>
+        <v>4.937614582406516</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6253,22 +6253,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.06858103633303735</v>
+        <v>0.06844327161542203</v>
       </c>
       <c r="C61">
-        <v>484.6064157412974</v>
+        <v>478.6997641030846</v>
       </c>
       <c r="D61">
-        <v>894.5354157412972</v>
+        <v>897.7597641030844</v>
       </c>
       <c r="E61">
-        <v>110.329</v>
+        <v>119.4599999999999</v>
       </c>
       <c r="F61">
-        <v>538.7289999999999</v>
+        <v>547.8599999999999</v>
       </c>
       <c r="G61">
         <v>128.8</v>
@@ -6289,28 +6289,28 @@
         <v>147.1</v>
       </c>
       <c r="M61">
-        <v>29.7917137</v>
+        <v>30.296658</v>
       </c>
       <c r="N61">
-        <v>117.3082863</v>
+        <v>116.803342</v>
       </c>
       <c r="O61">
-        <v>31.67323730099999</v>
+        <v>31.53690233999999</v>
       </c>
       <c r="P61">
-        <v>85.63504899899996</v>
+        <v>85.26643965999997</v>
       </c>
       <c r="Q61">
-        <v>113.035048999</v>
+        <v>112.66643966</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1091788447147252</v>
+        <v>0.1105546790385551</v>
       </c>
       <c r="T61">
-        <v>1.160805798681099</v>
+        <v>1.1860046874951</v>
       </c>
       <c r="U61">
         <v>0.0553</v>
@@ -6327,7 +6327,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>4.937614582406516</v>
+        <v>4.855321006033074</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6335,22 +6335,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.06844327161542203</v>
+        <v>0.06830550689780671</v>
       </c>
       <c r="C62">
-        <v>478.6997641030846</v>
+        <v>472.8164408464856</v>
       </c>
       <c r="D62">
-        <v>897.7597641030844</v>
+        <v>901.0074408464857</v>
       </c>
       <c r="E62">
-        <v>119.4599999999999</v>
+        <v>128.591</v>
       </c>
       <c r="F62">
-        <v>547.8599999999999</v>
+        <v>556.991</v>
       </c>
       <c r="G62">
         <v>128.8</v>
@@ -6371,28 +6371,28 @@
         <v>147.1</v>
       </c>
       <c r="M62">
-        <v>30.296658</v>
+        <v>30.8016023</v>
       </c>
       <c r="N62">
-        <v>116.803342</v>
+        <v>116.2983977</v>
       </c>
       <c r="O62">
-        <v>31.53690233999999</v>
+        <v>31.40056737899999</v>
       </c>
       <c r="P62">
-        <v>85.26643965999997</v>
+        <v>84.89783032099997</v>
       </c>
       <c r="Q62">
-        <v>112.66643966</v>
+        <v>112.297830321</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1105546790385551</v>
+        <v>0.1120010689687351</v>
       </c>
       <c r="T62">
-        <v>1.1860046874951</v>
+        <v>1.21249582701751</v>
       </c>
       <c r="U62">
         <v>0.0553</v>
@@ -6409,7 +6409,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>4.855321006033074</v>
+        <v>4.775725579704662</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6417,22 +6417,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.06830550689780671</v>
+        <v>0.06816774218019138</v>
       </c>
       <c r="C63">
-        <v>472.8164408464856</v>
+        <v>466.9567000643523</v>
       </c>
       <c r="D63">
-        <v>901.0074408464857</v>
+        <v>904.2787000643522</v>
       </c>
       <c r="E63">
-        <v>128.591</v>
+        <v>137.722</v>
       </c>
       <c r="F63">
-        <v>556.991</v>
+        <v>566.122</v>
       </c>
       <c r="G63">
         <v>128.8</v>
@@ -6453,28 +6453,28 @@
         <v>147.1</v>
       </c>
       <c r="M63">
-        <v>30.8016023</v>
+        <v>31.3065466</v>
       </c>
       <c r="N63">
-        <v>116.2983977</v>
+        <v>115.7934534</v>
       </c>
       <c r="O63">
-        <v>31.40056737899999</v>
+        <v>31.264232418</v>
       </c>
       <c r="P63">
-        <v>84.89783032099997</v>
+        <v>84.52922098199998</v>
       </c>
       <c r="Q63">
-        <v>112.297830321</v>
+        <v>111.929220982</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1120010689687351</v>
+        <v>0.1135235846847142</v>
       </c>
       <c r="T63">
-        <v>1.21249582701751</v>
+        <v>1.2403812370411</v>
       </c>
       <c r="U63">
         <v>0.0553</v>
@@ -6491,7 +6491,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>4.775725579704662</v>
+        <v>4.698697747773943</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6499,22 +6499,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.06816774218019138</v>
+        <v>0.06802997746257605</v>
       </c>
       <c r="C64">
-        <v>466.9567000643523</v>
+        <v>461.1207995530904</v>
       </c>
       <c r="D64">
-        <v>904.2787000643522</v>
+        <v>907.5737995530903</v>
       </c>
       <c r="E64">
-        <v>137.722</v>
+        <v>146.853</v>
       </c>
       <c r="F64">
-        <v>566.122</v>
+        <v>575.2529999999999</v>
       </c>
       <c r="G64">
         <v>128.8</v>
@@ -6535,28 +6535,28 @@
         <v>147.1</v>
       </c>
       <c r="M64">
-        <v>31.3065466</v>
+        <v>31.8114909</v>
       </c>
       <c r="N64">
-        <v>115.7934534</v>
+        <v>115.2885091</v>
       </c>
       <c r="O64">
-        <v>31.264232418</v>
+        <v>31.12789745699999</v>
       </c>
       <c r="P64">
-        <v>84.52922098199998</v>
+        <v>84.16061164299998</v>
       </c>
       <c r="Q64">
-        <v>111.929220982</v>
+        <v>111.560611643</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1135235846847142</v>
+        <v>0.1151283985475028</v>
       </c>
       <c r="T64">
-        <v>1.2403812370411</v>
+        <v>1.269773966525425</v>
       </c>
       <c r="U64">
         <v>0.0553</v>
@@ -6573,7 +6573,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>4.698697747773943</v>
+        <v>4.624115243841024</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6581,22 +6581,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.06802997746257605</v>
+        <v>0.06789221274496074</v>
       </c>
       <c r="C65">
-        <v>461.1207995530904</v>
+        <v>455.3090008803825</v>
       </c>
       <c r="D65">
-        <v>907.5737995530903</v>
+        <v>910.8930008803825</v>
       </c>
       <c r="E65">
-        <v>146.853</v>
+        <v>155.9839999999999</v>
       </c>
       <c r="F65">
-        <v>575.2529999999999</v>
+        <v>584.3839999999999</v>
       </c>
       <c r="G65">
         <v>128.8</v>
@@ -6617,28 +6617,28 @@
         <v>147.1</v>
       </c>
       <c r="M65">
-        <v>31.8114909</v>
+        <v>32.31643519999999</v>
       </c>
       <c r="N65">
-        <v>115.2885091</v>
+        <v>114.7835648</v>
       </c>
       <c r="O65">
-        <v>31.12789745699999</v>
+        <v>30.99156249599999</v>
       </c>
       <c r="P65">
-        <v>84.16061164299998</v>
+        <v>83.79200230399996</v>
       </c>
       <c r="Q65">
-        <v>111.560611643</v>
+        <v>111.192002304</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1151283985475028</v>
+        <v>0.116822368736002</v>
       </c>
       <c r="T65">
-        <v>1.269773966525425</v>
+        <v>1.300799625425546</v>
       </c>
       <c r="U65">
         <v>0.0553</v>
@@ -6655,7 +6655,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>4.624115243841024</v>
+        <v>4.551863443156007</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6663,22 +6663,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.06789221274496074</v>
+        <v>0.06894069802734541</v>
       </c>
       <c r="C66">
-        <v>455.3090008803825</v>
+        <v>421.5107725639481</v>
       </c>
       <c r="D66">
-        <v>910.8930008803825</v>
+        <v>886.225772563948</v>
       </c>
       <c r="E66">
-        <v>155.9839999999999</v>
+        <v>165.115</v>
       </c>
       <c r="F66">
-        <v>584.3839999999999</v>
+        <v>593.515</v>
       </c>
       <c r="G66">
         <v>128.8</v>
@@ -6699,45 +6699,45 @@
         <v>147.1</v>
       </c>
       <c r="M66">
-        <v>32.31643519999999</v>
+        <v>34.305167</v>
       </c>
       <c r="N66">
-        <v>114.7835648</v>
+        <v>112.794833</v>
       </c>
       <c r="O66">
-        <v>30.99156249599999</v>
+        <v>30.45460490999999</v>
       </c>
       <c r="P66">
-        <v>83.79200230399996</v>
+        <v>82.34022808999997</v>
       </c>
       <c r="Q66">
-        <v>111.192002304</v>
+        <v>109.74022809</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.116822368736002</v>
+        <v>0.1186131372209869</v>
       </c>
       <c r="T66">
-        <v>1.300799625425546</v>
+        <v>1.333598179119959</v>
       </c>
       <c r="U66">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V66">
         <v>0.27</v>
       </c>
       <c r="W66">
-        <v>0.040369</v>
+        <v>0.042194</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y66">
-        <v>4.551863443156007</v>
+        <v>4.287983789730566</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6745,22 +6745,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.06894069802734541</v>
+        <v>0.0688211833097301</v>
       </c>
       <c r="C67">
-        <v>421.5107725639481</v>
+        <v>415.1238671679776</v>
       </c>
       <c r="D67">
-        <v>886.225772563948</v>
+        <v>888.9698671679774</v>
       </c>
       <c r="E67">
-        <v>165.115</v>
+        <v>174.246</v>
       </c>
       <c r="F67">
-        <v>593.515</v>
+        <v>602.646</v>
       </c>
       <c r="G67">
         <v>128.8</v>
@@ -6781,28 +6781,28 @@
         <v>147.1</v>
       </c>
       <c r="M67">
-        <v>34.305167</v>
+        <v>34.8329388</v>
       </c>
       <c r="N67">
-        <v>112.794833</v>
+        <v>112.2670612</v>
       </c>
       <c r="O67">
-        <v>30.45460490999999</v>
+        <v>30.31210652399999</v>
       </c>
       <c r="P67">
-        <v>82.34022808999997</v>
+        <v>81.95495467599997</v>
       </c>
       <c r="Q67">
-        <v>109.74022809</v>
+        <v>109.354954676</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1186131372209869</v>
+        <v>0.1205092450286179</v>
       </c>
       <c r="T67">
-        <v>1.333598179119959</v>
+        <v>1.368326059502278</v>
       </c>
       <c r="U67">
         <v>0.0578</v>
@@ -6819,7 +6819,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>4.287983789730566</v>
+        <v>4.223014338371012</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6827,22 +6827,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.0688211833097301</v>
+        <v>0.06870166859211478</v>
       </c>
       <c r="C68">
-        <v>415.1238671679776</v>
+        <v>408.7540080908697</v>
       </c>
       <c r="D68">
-        <v>888.9698671679774</v>
+        <v>891.7310080908696</v>
       </c>
       <c r="E68">
-        <v>174.246</v>
+        <v>183.377</v>
       </c>
       <c r="F68">
-        <v>602.646</v>
+        <v>611.7769999999999</v>
       </c>
       <c r="G68">
         <v>128.8</v>
@@ -6863,28 +6863,28 @@
         <v>147.1</v>
       </c>
       <c r="M68">
-        <v>34.8329388</v>
+        <v>35.3607106</v>
       </c>
       <c r="N68">
-        <v>112.2670612</v>
+        <v>111.7392894</v>
       </c>
       <c r="O68">
-        <v>30.31210652399999</v>
+        <v>30.16960813799999</v>
       </c>
       <c r="P68">
-        <v>81.95495467599997</v>
+        <v>81.56968126199997</v>
       </c>
       <c r="Q68">
-        <v>109.354954676</v>
+        <v>108.969681262</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1205092450286179</v>
+        <v>0.1225202684609539</v>
       </c>
       <c r="T68">
-        <v>1.368326059502278</v>
+        <v>1.405158659907769</v>
       </c>
       <c r="U68">
         <v>0.0578</v>
@@ -6901,7 +6901,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>4.223014338371012</v>
+        <v>4.159984273619207</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6909,22 +6909,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.06870166859211478</v>
+        <v>0.06858215387449945</v>
       </c>
       <c r="C69">
-        <v>408.7540080908697</v>
+        <v>402.4013546651403</v>
       </c>
       <c r="D69">
-        <v>891.7310080908696</v>
+        <v>894.5093546651403</v>
       </c>
       <c r="E69">
-        <v>183.377</v>
+        <v>192.508</v>
       </c>
       <c r="F69">
-        <v>611.7769999999999</v>
+        <v>620.908</v>
       </c>
       <c r="G69">
         <v>128.8</v>
@@ -6945,28 +6945,28 @@
         <v>147.1</v>
       </c>
       <c r="M69">
-        <v>35.3607106</v>
+        <v>35.8884824</v>
       </c>
       <c r="N69">
-        <v>111.7392894</v>
+        <v>111.2115176</v>
       </c>
       <c r="O69">
-        <v>30.16960813799999</v>
+        <v>30.02710975199999</v>
       </c>
       <c r="P69">
-        <v>81.56968126199997</v>
+        <v>81.18440784799998</v>
       </c>
       <c r="Q69">
-        <v>108.969681262</v>
+        <v>108.584407848</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1225202684609539</v>
+        <v>0.1246569808578108</v>
       </c>
       <c r="T69">
-        <v>1.405158659907769</v>
+        <v>1.444293297838603</v>
       </c>
       <c r="U69">
         <v>0.0578</v>
@@ -6983,7 +6983,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>4.159984273619207</v>
+        <v>4.098808034301276</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6991,22 +6991,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.06858215387449945</v>
+        <v>0.06846263915688414</v>
       </c>
       <c r="C70">
-        <v>402.4013546651403</v>
+        <v>396.0660682152261</v>
       </c>
       <c r="D70">
-        <v>894.5093546651403</v>
+        <v>897.3050682152261</v>
       </c>
       <c r="E70">
-        <v>192.508</v>
+        <v>201.639</v>
       </c>
       <c r="F70">
-        <v>620.908</v>
+        <v>630.039</v>
       </c>
       <c r="G70">
         <v>128.8</v>
@@ -7027,28 +7027,28 @@
         <v>147.1</v>
       </c>
       <c r="M70">
-        <v>35.8884824</v>
+        <v>36.4162542</v>
       </c>
       <c r="N70">
-        <v>111.2115176</v>
+        <v>110.6837458</v>
       </c>
       <c r="O70">
-        <v>30.02710975199999</v>
+        <v>29.88461136599999</v>
       </c>
       <c r="P70">
-        <v>81.18440784799998</v>
+        <v>80.79913443399997</v>
       </c>
       <c r="Q70">
-        <v>108.584407848</v>
+        <v>108.199134434</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1246569808578108</v>
+        <v>0.1269315456673682</v>
       </c>
       <c r="T70">
-        <v>1.444293297838603</v>
+        <v>1.485952751119813</v>
       </c>
       <c r="U70">
         <v>0.0578</v>
@@ -7065,7 +7065,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>4.098808034301276</v>
+        <v>4.039405019311403</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7073,22 +7073,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.06846263915688414</v>
+        <v>0.07013162443926881</v>
       </c>
       <c r="C71">
-        <v>396.0660682152261</v>
+        <v>349.4096067428758</v>
       </c>
       <c r="D71">
-        <v>897.3050682152261</v>
+        <v>859.7796067428758</v>
       </c>
       <c r="E71">
-        <v>201.639</v>
+        <v>210.77</v>
       </c>
       <c r="F71">
-        <v>630.039</v>
+        <v>639.17</v>
       </c>
       <c r="G71">
         <v>128.8</v>
@@ -7109,45 +7109,45 @@
         <v>147.1</v>
       </c>
       <c r="M71">
-        <v>36.4162542</v>
+        <v>39.181121</v>
       </c>
       <c r="N71">
-        <v>110.6837458</v>
+        <v>107.918879</v>
       </c>
       <c r="O71">
-        <v>29.88461136599999</v>
+        <v>29.13809732999999</v>
       </c>
       <c r="P71">
-        <v>80.79913443399997</v>
+        <v>78.78078166999998</v>
       </c>
       <c r="Q71">
-        <v>108.199134434</v>
+        <v>106.18078167</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1269315456673682</v>
+        <v>0.129357748130896</v>
       </c>
       <c r="T71">
-        <v>1.485952751119813</v>
+        <v>1.530389501286438</v>
       </c>
       <c r="U71">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V71">
         <v>0.27</v>
       </c>
       <c r="W71">
-        <v>0.042194</v>
+        <v>0.044749</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y71">
-        <v>4.039405019311403</v>
+        <v>3.754359146590012</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7155,22 +7155,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.07013162443926881</v>
+        <v>0.07003765972165349</v>
       </c>
       <c r="C72">
-        <v>349.4096067428758</v>
+        <v>342.3077332193949</v>
       </c>
       <c r="D72">
-        <v>859.7796067428758</v>
+        <v>861.808733219395</v>
       </c>
       <c r="E72">
-        <v>210.77</v>
+        <v>219.9010000000001</v>
       </c>
       <c r="F72">
-        <v>639.17</v>
+        <v>648.301</v>
       </c>
       <c r="G72">
         <v>128.8</v>
@@ -7191,28 +7191,28 @@
         <v>147.1</v>
       </c>
       <c r="M72">
-        <v>39.181121</v>
+        <v>39.7408513</v>
       </c>
       <c r="N72">
-        <v>107.918879</v>
+        <v>107.3591487</v>
       </c>
       <c r="O72">
-        <v>29.13809732999999</v>
+        <v>28.98697014899999</v>
       </c>
       <c r="P72">
-        <v>78.78078166999998</v>
+        <v>78.37217855099998</v>
       </c>
       <c r="Q72">
-        <v>106.18078167</v>
+        <v>105.772178551</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.129357748130896</v>
+        <v>0.1319512749022534</v>
       </c>
       <c r="T72">
-        <v>1.530389501286438</v>
+        <v>1.577890854912829</v>
       </c>
       <c r="U72">
         <v>0.0613</v>
@@ -7229,7 +7229,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>3.754359146590012</v>
+        <v>3.701480848750715</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7237,22 +7237,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.07003765972165349</v>
+        <v>0.06994369500403816</v>
       </c>
       <c r="C73">
-        <v>342.307733219395</v>
+        <v>335.2154600502191</v>
       </c>
       <c r="D73">
-        <v>861.808733219395</v>
+        <v>863.8474600502191</v>
       </c>
       <c r="E73">
-        <v>219.901</v>
+        <v>229.0319999999999</v>
       </c>
       <c r="F73">
-        <v>648.3009999999999</v>
+        <v>657.4319999999999</v>
       </c>
       <c r="G73">
         <v>128.8</v>
@@ -7273,28 +7273,28 @@
         <v>147.1</v>
       </c>
       <c r="M73">
-        <v>39.7408513</v>
+        <v>40.30058159999999</v>
       </c>
       <c r="N73">
-        <v>107.3591487</v>
+        <v>106.7994184</v>
       </c>
       <c r="O73">
-        <v>28.98697014899999</v>
+        <v>28.835842968</v>
       </c>
       <c r="P73">
-        <v>78.37217855099998</v>
+        <v>77.96357543199998</v>
       </c>
       <c r="Q73">
-        <v>105.772178551</v>
+        <v>105.363575432</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1319512749022534</v>
+        <v>0.1347300535858506</v>
       </c>
       <c r="T73">
-        <v>1.577890854912829</v>
+        <v>1.628785162369677</v>
       </c>
       <c r="U73">
         <v>0.0613</v>
@@ -7311,7 +7311,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>3.701480848750716</v>
+        <v>3.650071392518067</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7319,22 +7319,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.06994369500403816</v>
+        <v>0.06984973028642284</v>
       </c>
       <c r="C74">
-        <v>335.2154600502191</v>
+        <v>328.1328555297741</v>
       </c>
       <c r="D74">
-        <v>863.8474600502191</v>
+        <v>865.8958555297741</v>
       </c>
       <c r="E74">
-        <v>229.0319999999999</v>
+        <v>238.1629999999999</v>
       </c>
       <c r="F74">
-        <v>657.4319999999999</v>
+        <v>666.5629999999999</v>
       </c>
       <c r="G74">
         <v>128.8</v>
@@ -7355,28 +7355,28 @@
         <v>147.1</v>
       </c>
       <c r="M74">
-        <v>40.30058159999999</v>
+        <v>40.86031189999999</v>
       </c>
       <c r="N74">
-        <v>106.7994184</v>
+        <v>106.2396881</v>
       </c>
       <c r="O74">
-        <v>28.835842968</v>
+        <v>28.68471578699999</v>
       </c>
       <c r="P74">
-        <v>77.96357543199998</v>
+        <v>77.55497231299998</v>
       </c>
       <c r="Q74">
-        <v>105.363575432</v>
+        <v>104.954972313</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1347300535858506</v>
+        <v>0.137714667727492</v>
       </c>
       <c r="T74">
-        <v>1.628785162369677</v>
+        <v>1.683449418527031</v>
       </c>
       <c r="U74">
         <v>0.0613</v>
@@ -7393,7 +7393,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>3.650071392518067</v>
+        <v>3.600070414538367</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7401,22 +7401,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.06984973028642284</v>
+        <v>0.06975576556880753</v>
       </c>
       <c r="C75">
-        <v>328.1328555297741</v>
+        <v>321.0599886017983</v>
       </c>
       <c r="D75">
-        <v>865.8958555297741</v>
+        <v>867.9539886017983</v>
       </c>
       <c r="E75">
-        <v>238.1629999999999</v>
+        <v>247.294</v>
       </c>
       <c r="F75">
-        <v>666.5629999999999</v>
+        <v>675.694</v>
       </c>
       <c r="G75">
         <v>128.8</v>
@@ -7437,28 +7437,28 @@
         <v>147.1</v>
       </c>
       <c r="M75">
-        <v>40.86031189999999</v>
+        <v>41.4200422</v>
       </c>
       <c r="N75">
-        <v>106.2396881</v>
+        <v>105.6799578</v>
       </c>
       <c r="O75">
-        <v>28.68471578699999</v>
+        <v>28.533588606</v>
       </c>
       <c r="P75">
-        <v>77.55497231299998</v>
+        <v>77.14636919399997</v>
       </c>
       <c r="Q75">
-        <v>104.954972313</v>
+        <v>104.546369194</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.137714667727492</v>
+        <v>0.1409288675723366</v>
       </c>
       <c r="T75">
-        <v>1.683449418527031</v>
+        <v>1.742318617465722</v>
       </c>
       <c r="U75">
         <v>0.0613</v>
@@ -7475,7 +7475,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>3.600070414538367</v>
+        <v>3.551420814341903</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7483,22 +7483,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.06975576556880753</v>
+        <v>0.0696618008511922</v>
       </c>
       <c r="C76">
-        <v>321.0599886017983</v>
+        <v>313.9969288670771</v>
       </c>
       <c r="D76">
-        <v>867.9539886017983</v>
+        <v>870.0219288670771</v>
       </c>
       <c r="E76">
-        <v>247.294</v>
+        <v>256.425</v>
       </c>
       <c r="F76">
-        <v>675.694</v>
+        <v>684.8249999999999</v>
       </c>
       <c r="G76">
         <v>128.8</v>
@@ -7519,28 +7519,28 @@
         <v>147.1</v>
       </c>
       <c r="M76">
-        <v>41.4200422</v>
+        <v>41.9797725</v>
       </c>
       <c r="N76">
-        <v>105.6799578</v>
+        <v>105.1202275</v>
       </c>
       <c r="O76">
-        <v>28.533588606</v>
+        <v>28.382461425</v>
       </c>
       <c r="P76">
-        <v>77.14636919399997</v>
+        <v>76.73776607499997</v>
       </c>
       <c r="Q76">
-        <v>104.546369194</v>
+        <v>104.137766075</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.1409288675723366</v>
+        <v>0.1444002034047688</v>
       </c>
       <c r="T76">
-        <v>1.742318617465722</v>
+        <v>1.805897352319507</v>
       </c>
       <c r="U76">
         <v>0.0613</v>
@@ -7557,7 +7557,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>3.551420814341903</v>
+        <v>3.504068536817344</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7565,22 +7565,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.0696618008511922</v>
+        <v>0.07112127613357688</v>
       </c>
       <c r="C77">
-        <v>313.9969288670771</v>
+        <v>273.8187524677764</v>
       </c>
       <c r="D77">
-        <v>870.0219288670771</v>
+        <v>838.9747524677763</v>
       </c>
       <c r="E77">
-        <v>256.425</v>
+        <v>265.5559999999999</v>
       </c>
       <c r="F77">
-        <v>684.8249999999999</v>
+        <v>693.9559999999999</v>
       </c>
       <c r="G77">
         <v>128.8</v>
@@ -7601,45 +7601,45 @@
         <v>147.1</v>
       </c>
       <c r="M77">
-        <v>41.9797725</v>
+        <v>44.48257959999999</v>
       </c>
       <c r="N77">
-        <v>105.1202275</v>
+        <v>102.6174204</v>
       </c>
       <c r="O77">
-        <v>28.382461425</v>
+        <v>27.70670350799999</v>
       </c>
       <c r="P77">
-        <v>76.73776607499997</v>
+        <v>74.91071689199998</v>
       </c>
       <c r="Q77">
-        <v>104.137766075</v>
+        <v>102.310716892</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.1444002034047688</v>
+        <v>0.148160817223237</v>
       </c>
       <c r="T77">
-        <v>1.805897352319507</v>
+        <v>1.874774315077775</v>
       </c>
       <c r="U77">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V77">
         <v>0.27</v>
       </c>
       <c r="W77">
-        <v>0.044749</v>
+        <v>0.046793</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y77">
-        <v>3.504068536817344</v>
+        <v>3.306912533462875</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7647,22 +7647,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.07112127613357688</v>
+        <v>0.07104775141596156</v>
       </c>
       <c r="C78">
-        <v>273.8187524677764</v>
+        <v>266.1987330280087</v>
       </c>
       <c r="D78">
-        <v>838.9747524677763</v>
+        <v>840.4857330280088</v>
       </c>
       <c r="E78">
-        <v>265.5559999999999</v>
+        <v>274.687</v>
       </c>
       <c r="F78">
-        <v>693.9559999999999</v>
+        <v>703.087</v>
       </c>
       <c r="G78">
         <v>128.8</v>
@@ -7683,28 +7683,28 @@
         <v>147.1</v>
       </c>
       <c r="M78">
-        <v>44.48257959999999</v>
+        <v>45.0678767</v>
       </c>
       <c r="N78">
-        <v>102.6174204</v>
+        <v>102.0321233</v>
       </c>
       <c r="O78">
-        <v>27.70670350799999</v>
+        <v>27.54867329099999</v>
       </c>
       <c r="P78">
-        <v>74.91071689199998</v>
+        <v>74.48345000899997</v>
       </c>
       <c r="Q78">
-        <v>102.310716892</v>
+        <v>101.883450009</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.148160817223237</v>
+        <v>0.1522484409389633</v>
       </c>
       <c r="T78">
-        <v>1.874774315077775</v>
+        <v>1.949640578945457</v>
       </c>
       <c r="U78">
         <v>0.0641</v>
@@ -7721,7 +7721,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>3.306912533462875</v>
+        <v>3.263965617443876</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7729,22 +7729,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.07104775141596156</v>
+        <v>0.07097422669834624</v>
       </c>
       <c r="C79">
-        <v>266.1987330280087</v>
+        <v>258.5841659130577</v>
       </c>
       <c r="D79">
-        <v>840.4857330280088</v>
+        <v>842.0021659130578</v>
       </c>
       <c r="E79">
-        <v>274.687</v>
+        <v>283.818</v>
       </c>
       <c r="F79">
-        <v>703.087</v>
+        <v>712.218</v>
       </c>
       <c r="G79">
         <v>128.8</v>
@@ -7765,28 +7765,28 @@
         <v>147.1</v>
       </c>
       <c r="M79">
-        <v>45.0678767</v>
+        <v>45.6531738</v>
       </c>
       <c r="N79">
-        <v>102.0321233</v>
+        <v>101.4468262</v>
       </c>
       <c r="O79">
-        <v>27.54867329099999</v>
+        <v>27.390643074</v>
       </c>
       <c r="P79">
-        <v>74.48345000899997</v>
+        <v>74.05618312599998</v>
       </c>
       <c r="Q79">
-        <v>101.883450009</v>
+        <v>101.456183126</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.1522484409389633</v>
+        <v>0.1567076668106647</v>
       </c>
       <c r="T79">
-        <v>1.949640578945457</v>
+        <v>2.03131286680111</v>
       </c>
       <c r="U79">
         <v>0.0641</v>
@@ -7803,7 +7803,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>3.263965617443876</v>
+        <v>3.222119904399724</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7811,22 +7811,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.07097422669834624</v>
+        <v>0.07090070198073092</v>
       </c>
       <c r="C80">
-        <v>258.5841659130577</v>
+        <v>250.975080688075</v>
       </c>
       <c r="D80">
-        <v>842.0021659130578</v>
+        <v>843.5240806880748</v>
       </c>
       <c r="E80">
-        <v>283.818</v>
+        <v>292.949</v>
       </c>
       <c r="F80">
-        <v>712.218</v>
+        <v>721.3489999999999</v>
       </c>
       <c r="G80">
         <v>128.8</v>
@@ -7847,28 +7847,28 @@
         <v>147.1</v>
       </c>
       <c r="M80">
-        <v>45.6531738</v>
+        <v>46.2384709</v>
       </c>
       <c r="N80">
-        <v>101.4468262</v>
+        <v>100.8615291</v>
       </c>
       <c r="O80">
-        <v>27.390643074</v>
+        <v>27.23261285699999</v>
       </c>
       <c r="P80">
-        <v>74.05618312599998</v>
+        <v>73.62891624299998</v>
       </c>
       <c r="Q80">
-        <v>101.456183126</v>
+        <v>101.028916243</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.1567076668106647</v>
+        <v>0.1615915808606234</v>
       </c>
       <c r="T80">
-        <v>2.03131286680111</v>
+        <v>2.120763467785873</v>
       </c>
       <c r="U80">
         <v>0.0641</v>
@@ -7885,7 +7885,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>3.222119904399724</v>
+        <v>3.18133357649593</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7893,22 +7893,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.07090070198073092</v>
+        <v>0.07082717726311558</v>
       </c>
       <c r="C81">
-        <v>250.975080688075</v>
+        <v>243.3715071323536</v>
       </c>
       <c r="D81">
-        <v>843.5240806880748</v>
+        <v>845.0515071323535</v>
       </c>
       <c r="E81">
-        <v>292.949</v>
+        <v>302.08</v>
       </c>
       <c r="F81">
-        <v>721.3489999999999</v>
+        <v>730.48</v>
       </c>
       <c r="G81">
         <v>128.8</v>
@@ -7929,28 +7929,28 @@
         <v>147.1</v>
       </c>
       <c r="M81">
-        <v>46.2384709</v>
+        <v>46.823768</v>
       </c>
       <c r="N81">
-        <v>100.8615291</v>
+        <v>100.276232</v>
       </c>
       <c r="O81">
-        <v>27.23261285699999</v>
+        <v>27.07458263999999</v>
       </c>
       <c r="P81">
-        <v>73.62891624299998</v>
+        <v>73.20164935999998</v>
       </c>
       <c r="Q81">
-        <v>101.028916243</v>
+        <v>100.60164936</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.1615915808606234</v>
+        <v>0.166963886315578</v>
       </c>
       <c r="T81">
-        <v>2.120763467785873</v>
+        <v>2.219159128869113</v>
       </c>
       <c r="U81">
         <v>0.0641</v>
@@ -7967,7 +7967,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>3.18133357649593</v>
+        <v>3.14156690678973</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7975,22 +7975,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.07082717726311558</v>
+        <v>0.07075365254550027</v>
       </c>
       <c r="C82">
-        <v>243.3715071323536</v>
+        <v>235.7734752412708</v>
       </c>
       <c r="D82">
-        <v>845.0515071323535</v>
+        <v>846.5844752412709</v>
       </c>
       <c r="E82">
-        <v>302.08</v>
+        <v>311.211</v>
       </c>
       <c r="F82">
-        <v>730.48</v>
+        <v>739.611</v>
       </c>
       <c r="G82">
         <v>128.8</v>
@@ -8011,28 +8011,28 @@
         <v>147.1</v>
       </c>
       <c r="M82">
-        <v>46.823768</v>
+        <v>47.4090651</v>
       </c>
       <c r="N82">
-        <v>100.276232</v>
+        <v>99.69093489999997</v>
       </c>
       <c r="O82">
-        <v>27.07458263999999</v>
+        <v>26.916552423</v>
       </c>
       <c r="P82">
-        <v>73.20164935999998</v>
+        <v>72.77438247699997</v>
       </c>
       <c r="Q82">
-        <v>100.60164936</v>
+        <v>100.174382477</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.166963886315578</v>
+        <v>0.1729016976078962</v>
       </c>
       <c r="T82">
-        <v>2.219159128869113</v>
+        <v>2.327912227961114</v>
       </c>
       <c r="U82">
         <v>0.0641</v>
@@ -8049,7 +8049,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>3.14156690678973</v>
+        <v>3.102782130162697</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8057,22 +8057,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.07075365254550027</v>
+        <v>0.07068012782788495</v>
       </c>
       <c r="C83">
-        <v>235.7734752412708</v>
+        <v>228.1810152282546</v>
       </c>
       <c r="D83">
-        <v>846.5844752412709</v>
+        <v>848.1230152282545</v>
       </c>
       <c r="E83">
-        <v>311.211</v>
+        <v>320.342</v>
       </c>
       <c r="F83">
-        <v>739.611</v>
+        <v>748.742</v>
       </c>
       <c r="G83">
         <v>128.8</v>
@@ -8093,28 +8093,28 @@
         <v>147.1</v>
       </c>
       <c r="M83">
-        <v>47.4090651</v>
+        <v>47.9943622</v>
       </c>
       <c r="N83">
-        <v>99.69093489999997</v>
+        <v>99.10563779999997</v>
       </c>
       <c r="O83">
-        <v>26.916552423</v>
+        <v>26.75852220599999</v>
       </c>
       <c r="P83">
-        <v>72.77438247699997</v>
+        <v>72.34711559399997</v>
       </c>
       <c r="Q83">
-        <v>100.174382477</v>
+        <v>99.74711559399996</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.1729016976078962</v>
+        <v>0.179499265710472</v>
       </c>
       <c r="T83">
-        <v>2.327912227961114</v>
+        <v>2.448749004730005</v>
       </c>
       <c r="U83">
         <v>0.0641</v>
@@ -8131,7 +8131,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>3.102782130162697</v>
+        <v>3.064943323697298</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8139,22 +8139,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.07068012782788495</v>
+        <v>0.07060660311026963</v>
       </c>
       <c r="C84">
-        <v>228.1810152282546</v>
+        <v>220.5941575267642</v>
       </c>
       <c r="D84">
-        <v>848.1230152282545</v>
+        <v>849.6671575267642</v>
       </c>
       <c r="E84">
-        <v>320.342</v>
+        <v>329.473</v>
       </c>
       <c r="F84">
-        <v>748.742</v>
+        <v>757.8729999999999</v>
       </c>
       <c r="G84">
         <v>128.8</v>
@@ -8175,28 +8175,28 @@
         <v>147.1</v>
       </c>
       <c r="M84">
-        <v>47.9943622</v>
+        <v>48.5796593</v>
       </c>
       <c r="N84">
-        <v>99.10563779999997</v>
+        <v>98.52034069999996</v>
       </c>
       <c r="O84">
-        <v>26.75852220599999</v>
+        <v>26.60049198899999</v>
       </c>
       <c r="P84">
-        <v>72.34711559399997</v>
+        <v>71.91984871099997</v>
       </c>
       <c r="Q84">
-        <v>99.74711559399996</v>
+        <v>99.31984871099996</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.179499265710472</v>
+        <v>0.1868730182957038</v>
       </c>
       <c r="T84">
-        <v>2.448749004730005</v>
+        <v>2.583801872883471</v>
       </c>
       <c r="U84">
         <v>0.0641</v>
@@ -8213,7 +8213,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>3.064943323697298</v>
+        <v>3.028016295700945</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8221,22 +8221,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.07060660311026963</v>
+        <v>0.07531603839265433</v>
       </c>
       <c r="C85">
-        <v>220.5941575267642</v>
+        <v>122.7254267747875</v>
       </c>
       <c r="D85">
-        <v>849.6671575267642</v>
+        <v>760.9294267747874</v>
       </c>
       <c r="E85">
-        <v>329.473</v>
+        <v>338.604</v>
       </c>
       <c r="F85">
-        <v>757.8729999999999</v>
+        <v>767.004</v>
       </c>
       <c r="G85">
         <v>128.8</v>
@@ -8257,45 +8257,45 @@
         <v>147.1</v>
       </c>
       <c r="M85">
-        <v>48.5796593</v>
+        <v>55.14758760000001</v>
       </c>
       <c r="N85">
-        <v>98.52034069999996</v>
+        <v>91.95241239999996</v>
       </c>
       <c r="O85">
-        <v>26.60049198899999</v>
+        <v>24.82715134799999</v>
       </c>
       <c r="P85">
-        <v>71.91984871099997</v>
+        <v>67.12526105199997</v>
       </c>
       <c r="Q85">
-        <v>99.31984871099996</v>
+        <v>94.52526105199996</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.1868730182957038</v>
+        <v>0.1951684899540895</v>
       </c>
       <c r="T85">
-        <v>2.583801872883471</v>
+        <v>2.735736349556121</v>
       </c>
       <c r="U85">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V85">
         <v>0.27</v>
       </c>
       <c r="W85">
-        <v>0.046793</v>
+        <v>0.05248700000000001</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y85">
-        <v>3.028016295700945</v>
+        <v>2.667387757139171</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8303,22 +8303,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.07531603839265431</v>
+        <v>0.07529945367503899</v>
       </c>
       <c r="C86">
-        <v>122.7254267747878</v>
+        <v>113.8743912149122</v>
       </c>
       <c r="D86">
-        <v>760.9294267747877</v>
+        <v>761.209391214912</v>
       </c>
       <c r="E86">
-        <v>338.6039999999999</v>
+        <v>347.7349999999999</v>
       </c>
       <c r="F86">
-        <v>767.0039999999999</v>
+        <v>776.1349999999999</v>
       </c>
       <c r="G86">
         <v>128.8</v>
@@ -8339,28 +8339,28 @@
         <v>147.1</v>
       </c>
       <c r="M86">
-        <v>55.14758759999999</v>
+        <v>55.8041065</v>
       </c>
       <c r="N86">
-        <v>91.95241239999997</v>
+        <v>91.29589349999998</v>
       </c>
       <c r="O86">
-        <v>24.82715134799999</v>
+        <v>24.649891245</v>
       </c>
       <c r="P86">
-        <v>67.12526105199998</v>
+        <v>66.64600225499998</v>
       </c>
       <c r="Q86">
-        <v>94.52526105199998</v>
+        <v>94.04600225499998</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.1951684899540894</v>
+        <v>0.2045700245002599</v>
       </c>
       <c r="T86">
-        <v>2.735736349556118</v>
+        <v>2.907928756451787</v>
       </c>
       <c r="U86">
         <v>0.07190000000000001</v>
@@ -8377,7 +8377,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>2.667387757139172</v>
+        <v>2.63600672470224</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8385,22 +8385,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.07529945367503899</v>
+        <v>0.07528286895742367</v>
       </c>
       <c r="C87">
-        <v>113.8743912149122</v>
+        <v>105.0235617423117</v>
       </c>
       <c r="D87">
-        <v>761.209391214912</v>
+        <v>761.4895617423117</v>
       </c>
       <c r="E87">
-        <v>347.7349999999999</v>
+        <v>356.866</v>
       </c>
       <c r="F87">
-        <v>776.1349999999999</v>
+        <v>785.266</v>
       </c>
       <c r="G87">
         <v>128.8</v>
@@ -8421,28 +8421,28 @@
         <v>147.1</v>
       </c>
       <c r="M87">
-        <v>55.8041065</v>
+        <v>56.4606254</v>
       </c>
       <c r="N87">
-        <v>91.29589349999998</v>
+        <v>90.63937459999997</v>
       </c>
       <c r="O87">
-        <v>24.649891245</v>
+        <v>24.47263114199999</v>
       </c>
       <c r="P87">
-        <v>66.64600225499998</v>
+        <v>66.16674345799997</v>
       </c>
       <c r="Q87">
-        <v>94.04600225499998</v>
+        <v>93.56674345799996</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.2045700245002599</v>
+        <v>0.215314635410169</v>
       </c>
       <c r="T87">
-        <v>2.907928756451787</v>
+        <v>3.104720078618266</v>
       </c>
       <c r="U87">
         <v>0.07190000000000001</v>
@@ -8459,7 +8459,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>2.63600672470224</v>
+        <v>2.60535548371733</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8467,22 +8467,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.07528286895742367</v>
+        <v>0.07526628423980834</v>
       </c>
       <c r="C88">
-        <v>105.0235617423117</v>
+        <v>96.17293858462858</v>
       </c>
       <c r="D88">
-        <v>761.4895617423117</v>
+        <v>761.7699385846286</v>
       </c>
       <c r="E88">
-        <v>356.866</v>
+        <v>365.997</v>
       </c>
       <c r="F88">
-        <v>785.266</v>
+        <v>794.3969999999999</v>
       </c>
       <c r="G88">
         <v>128.8</v>
@@ -8503,28 +8503,28 @@
         <v>147.1</v>
       </c>
       <c r="M88">
-        <v>56.4606254</v>
+        <v>57.1171443</v>
       </c>
       <c r="N88">
-        <v>90.63937459999997</v>
+        <v>89.98285569999996</v>
       </c>
       <c r="O88">
-        <v>24.47263114199999</v>
+        <v>24.29537103899999</v>
       </c>
       <c r="P88">
-        <v>66.16674345799997</v>
+        <v>65.68748466099997</v>
       </c>
       <c r="Q88">
-        <v>93.56674345799996</v>
+        <v>93.08748466099996</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.215314635410169</v>
+        <v>0.2277122633831411</v>
       </c>
       <c r="T88">
-        <v>3.104720078618266</v>
+        <v>3.331786988810356</v>
       </c>
       <c r="U88">
         <v>0.07190000000000001</v>
@@ -8541,7 +8541,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>2.60535548371733</v>
+        <v>2.575408868961958</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8549,22 +8549,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.07526628423980834</v>
+        <v>0.07524969952219301</v>
       </c>
       <c r="C89">
-        <v>96.17293858462858</v>
+        <v>87.3225219698387</v>
       </c>
       <c r="D89">
-        <v>761.7699385846286</v>
+        <v>762.0505219698385</v>
       </c>
       <c r="E89">
-        <v>365.997</v>
+        <v>375.1279999999999</v>
       </c>
       <c r="F89">
-        <v>794.3969999999999</v>
+        <v>803.5279999999999</v>
       </c>
       <c r="G89">
         <v>128.8</v>
@@ -8585,28 +8585,28 @@
         <v>147.1</v>
       </c>
       <c r="M89">
-        <v>57.1171443</v>
+        <v>57.77366319999999</v>
       </c>
       <c r="N89">
-        <v>89.98285569999996</v>
+        <v>89.32633679999998</v>
       </c>
       <c r="O89">
-        <v>24.29537103899999</v>
+        <v>24.118110936</v>
       </c>
       <c r="P89">
-        <v>65.68748466099997</v>
+        <v>65.20822586399998</v>
       </c>
       <c r="Q89">
-        <v>93.08748466099996</v>
+        <v>92.60822586399998</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.2277122633831411</v>
+        <v>0.2421761626849418</v>
       </c>
       <c r="T89">
-        <v>3.331786988810356</v>
+        <v>3.596698384034463</v>
       </c>
       <c r="U89">
         <v>0.07190000000000001</v>
@@ -8623,7 +8623,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>2.575408868961958</v>
+        <v>2.546142859087391</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8631,22 +8631,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.07524969952219301</v>
+        <v>0.0752331148045777</v>
       </c>
       <c r="C90">
-        <v>87.3225219698387</v>
+        <v>78.47231212625434</v>
       </c>
       <c r="D90">
-        <v>762.0505219698385</v>
+        <v>762.3313121262541</v>
       </c>
       <c r="E90">
-        <v>375.1279999999999</v>
+        <v>384.2589999999999</v>
       </c>
       <c r="F90">
-        <v>803.5279999999999</v>
+        <v>812.6589999999999</v>
       </c>
       <c r="G90">
         <v>128.8</v>
@@ -8667,28 +8667,28 @@
         <v>147.1</v>
       </c>
       <c r="M90">
-        <v>57.77366319999999</v>
+        <v>58.4301821</v>
       </c>
       <c r="N90">
-        <v>89.32633679999998</v>
+        <v>88.66981789999997</v>
       </c>
       <c r="O90">
-        <v>24.118110936</v>
+        <v>23.94085083299999</v>
       </c>
       <c r="P90">
-        <v>65.20822586399998</v>
+        <v>64.72896706699999</v>
       </c>
       <c r="Q90">
-        <v>92.60822586399998</v>
+        <v>92.12896706699998</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.2421761626849418</v>
+        <v>0.2592698618597973</v>
       </c>
       <c r="T90">
-        <v>3.596698384034463</v>
+        <v>3.909775487481134</v>
       </c>
       <c r="U90">
         <v>0.07190000000000001</v>
@@ -8705,7 +8705,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>2.546142859087391</v>
+        <v>2.517534512356072</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8713,22 +8713,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.0752331148045777</v>
+        <v>0.07777883008696237</v>
       </c>
       <c r="C91">
-        <v>78.47231212625434</v>
+        <v>28.53287462707908</v>
       </c>
       <c r="D91">
-        <v>762.3313121262541</v>
+        <v>721.522874627079</v>
       </c>
       <c r="E91">
-        <v>384.2589999999999</v>
+        <v>393.39</v>
       </c>
       <c r="F91">
-        <v>812.6589999999999</v>
+        <v>821.79</v>
       </c>
       <c r="G91">
         <v>128.8</v>
@@ -8749,45 +8749,45 @@
         <v>147.1</v>
       </c>
       <c r="M91">
-        <v>58.4301821</v>
+        <v>62.291682</v>
       </c>
       <c r="N91">
-        <v>88.66981789999997</v>
+        <v>84.80831799999996</v>
       </c>
       <c r="O91">
-        <v>23.94085083299999</v>
+        <v>22.89824585999999</v>
       </c>
       <c r="P91">
-        <v>64.72896706699999</v>
+        <v>61.91007213999997</v>
       </c>
       <c r="Q91">
-        <v>92.12896706699998</v>
+        <v>89.31007213999996</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.2592698618597973</v>
+        <v>0.2797823008696238</v>
       </c>
       <c r="T91">
-        <v>3.909775487481134</v>
+        <v>4.285468011617139</v>
       </c>
       <c r="U91">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V91">
         <v>0.27</v>
       </c>
       <c r="W91">
-        <v>0.05248700000000001</v>
+        <v>0.055334</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y91">
-        <v>2.517534512356072</v>
+        <v>2.361470990621187</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8795,22 +8795,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.07777883008696237</v>
+        <v>0.07779071536934706</v>
       </c>
       <c r="C92">
-        <v>28.53287462707908</v>
+        <v>19.22159466388564</v>
       </c>
       <c r="D92">
-        <v>721.522874627079</v>
+        <v>721.3425946638855</v>
       </c>
       <c r="E92">
-        <v>393.39</v>
+        <v>402.521</v>
       </c>
       <c r="F92">
-        <v>821.79</v>
+        <v>830.9209999999999</v>
       </c>
       <c r="G92">
         <v>128.8</v>
@@ -8831,28 +8831,28 @@
         <v>147.1</v>
       </c>
       <c r="M92">
-        <v>62.291682</v>
+        <v>62.9838118</v>
       </c>
       <c r="N92">
-        <v>84.80831799999996</v>
+        <v>84.11618819999997</v>
       </c>
       <c r="O92">
-        <v>22.89824585999999</v>
+        <v>22.71137081399999</v>
       </c>
       <c r="P92">
-        <v>61.91007213999997</v>
+        <v>61.40481738599998</v>
       </c>
       <c r="Q92">
-        <v>89.31007213999996</v>
+        <v>88.80481738599997</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.2797823008696238</v>
+        <v>0.3048530596594118</v>
       </c>
       <c r="T92">
-        <v>4.285468011617139</v>
+        <v>4.744647763338923</v>
       </c>
       <c r="U92">
         <v>0.07580000000000001</v>
@@ -8869,7 +8869,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>2.361470990621187</v>
+        <v>2.335520759955021</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8877,22 +8877,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.07779071536934706</v>
+        <v>0.07780260065173174</v>
       </c>
       <c r="C93">
-        <v>19.22159466388564</v>
+        <v>9.910404767820182</v>
       </c>
       <c r="D93">
-        <v>721.3425946638855</v>
+        <v>721.1624047678201</v>
       </c>
       <c r="E93">
-        <v>402.521</v>
+        <v>411.6519999999999</v>
       </c>
       <c r="F93">
-        <v>830.9209999999999</v>
+        <v>840.0519999999999</v>
       </c>
       <c r="G93">
         <v>128.8</v>
@@ -8913,28 +8913,28 @@
         <v>147.1</v>
       </c>
       <c r="M93">
-        <v>62.9838118</v>
+        <v>63.6759416</v>
       </c>
       <c r="N93">
-        <v>84.11618819999997</v>
+        <v>83.42405839999996</v>
       </c>
       <c r="O93">
-        <v>22.71137081399999</v>
+        <v>22.52449576799999</v>
       </c>
       <c r="P93">
-        <v>61.40481738599998</v>
+        <v>60.89956263199997</v>
       </c>
       <c r="Q93">
-        <v>88.80481738599997</v>
+        <v>88.29956263199996</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.3048530596594118</v>
+        <v>0.3361915081466468</v>
       </c>
       <c r="T93">
-        <v>4.744647763338923</v>
+        <v>5.318622452991153</v>
       </c>
       <c r="U93">
         <v>0.07580000000000001</v>
@@ -8951,7 +8951,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>2.335520759955021</v>
+        <v>2.310134664738118</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8959,22 +8959,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.07780260065173174</v>
+        <v>0.07781448593411641</v>
       </c>
       <c r="C94">
-        <v>9.910404767820182</v>
+        <v>0.5993048714035467</v>
       </c>
       <c r="D94">
-        <v>721.1624047678201</v>
+        <v>720.9823048714036</v>
       </c>
       <c r="E94">
-        <v>411.6519999999999</v>
+        <v>420.783</v>
       </c>
       <c r="F94">
-        <v>840.0519999999999</v>
+        <v>849.183</v>
       </c>
       <c r="G94">
         <v>128.8</v>
@@ -8995,28 +8995,28 @@
         <v>147.1</v>
       </c>
       <c r="M94">
-        <v>63.6759416</v>
+        <v>64.36807140000001</v>
       </c>
       <c r="N94">
-        <v>83.42405839999996</v>
+        <v>82.73192859999996</v>
       </c>
       <c r="O94">
-        <v>22.52449576799999</v>
+        <v>22.33762072199999</v>
       </c>
       <c r="P94">
-        <v>60.89956263199997</v>
+        <v>60.39430787799997</v>
       </c>
       <c r="Q94">
-        <v>88.29956263199996</v>
+        <v>87.79430787799996</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.3361915081466468</v>
+        <v>0.3764837990588061</v>
       </c>
       <c r="T94">
-        <v>5.318622452991153</v>
+        <v>6.05658991111545</v>
       </c>
       <c r="U94">
         <v>0.07580000000000001</v>
@@ -9033,7 +9033,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>2.310134664738118</v>
+        <v>2.285294507052761</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9041,22 +9041,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.07781448593411641</v>
+        <v>0.0778263712165011</v>
       </c>
       <c r="C95">
-        <v>0.5993048714035467</v>
+        <v>-8.71170509277556</v>
       </c>
       <c r="D95">
-        <v>720.9823048714036</v>
+        <v>720.8022949072243</v>
       </c>
       <c r="E95">
-        <v>420.783</v>
+        <v>429.914</v>
       </c>
       <c r="F95">
-        <v>849.183</v>
+        <v>858.314</v>
       </c>
       <c r="G95">
         <v>128.8</v>
@@ -9077,28 +9077,28 @@
         <v>147.1</v>
       </c>
       <c r="M95">
-        <v>64.36807140000001</v>
+        <v>65.06020120000001</v>
       </c>
       <c r="N95">
-        <v>82.73192859999996</v>
+        <v>82.03979879999996</v>
       </c>
       <c r="O95">
-        <v>22.33762072199999</v>
+        <v>22.15074567599999</v>
       </c>
       <c r="P95">
-        <v>60.39430787799997</v>
+        <v>59.88905312399997</v>
       </c>
       <c r="Q95">
-        <v>87.79430787799996</v>
+        <v>87.28905312399996</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.3764837990588061</v>
+        <v>0.4302068536083519</v>
       </c>
       <c r="T95">
-        <v>6.05658991111545</v>
+        <v>7.040546521947845</v>
       </c>
       <c r="U95">
         <v>0.07580000000000001</v>
@@ -9115,7 +9115,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>2.285294507052761</v>
+        <v>2.260982863360711</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9123,22 +9123,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.0778263712165011</v>
+        <v>0.07783825649888577</v>
       </c>
       <c r="C96">
-        <v>-8.71170509277556</v>
+        <v>-18.02262519206147</v>
       </c>
       <c r="D96">
-        <v>720.8022949072243</v>
+        <v>720.6223748079384</v>
       </c>
       <c r="E96">
-        <v>429.914</v>
+        <v>439.045</v>
       </c>
       <c r="F96">
-        <v>858.314</v>
+        <v>867.4449999999999</v>
       </c>
       <c r="G96">
         <v>128.8</v>
@@ -9159,28 +9159,28 @@
         <v>147.1</v>
       </c>
       <c r="M96">
-        <v>65.06020120000001</v>
+        <v>65.752331</v>
       </c>
       <c r="N96">
-        <v>82.03979879999996</v>
+        <v>81.34766899999997</v>
       </c>
       <c r="O96">
-        <v>22.15074567599999</v>
+        <v>21.96387062999999</v>
       </c>
       <c r="P96">
-        <v>59.88905312399997</v>
+        <v>59.38379836999998</v>
       </c>
       <c r="Q96">
-        <v>87.28905312399996</v>
+        <v>86.78379836999997</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.4302068536083519</v>
+        <v>0.505419129977716</v>
       </c>
       <c r="T96">
-        <v>7.040546521947845</v>
+        <v>8.4180857771132</v>
       </c>
       <c r="U96">
         <v>0.07580000000000001</v>
@@ -9197,7 +9197,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>2.260982863360711</v>
+        <v>2.237183043746388</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9205,22 +9205,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.07783825649888577</v>
+        <v>0.07785014178127043</v>
       </c>
       <c r="C97">
-        <v>-18.02262519206147</v>
+        <v>-27.33345549373098</v>
       </c>
       <c r="D97">
-        <v>720.6223748079384</v>
+        <v>720.442544506269</v>
       </c>
       <c r="E97">
-        <v>439.045</v>
+        <v>448.176</v>
       </c>
       <c r="F97">
-        <v>867.4449999999999</v>
+        <v>876.576</v>
       </c>
       <c r="G97">
         <v>128.8</v>
@@ -9241,28 +9241,28 @@
         <v>147.1</v>
       </c>
       <c r="M97">
-        <v>65.752331</v>
+        <v>66.4444608</v>
       </c>
       <c r="N97">
-        <v>81.34766899999997</v>
+        <v>80.65553919999996</v>
       </c>
       <c r="O97">
-        <v>21.96387062999999</v>
+        <v>21.77699558399999</v>
       </c>
       <c r="P97">
-        <v>59.38379836999998</v>
+        <v>58.87854361599997</v>
       </c>
       <c r="Q97">
-        <v>86.78379836999997</v>
+        <v>86.27854361599996</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.505419129977716</v>
+        <v>0.6182375445317621</v>
       </c>
       <c r="T97">
-        <v>8.4180857771132</v>
+        <v>10.48439465986123</v>
       </c>
       <c r="U97">
         <v>0.07580000000000001</v>
@@ -9279,7 +9279,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>2.237183043746388</v>
+        <v>2.213879053707362</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9287,22 +9287,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.07785014178127045</v>
+        <v>0.07786202706365514</v>
       </c>
       <c r="C98">
-        <v>-27.33345549373109</v>
+        <v>-36.6441960649945</v>
       </c>
       <c r="D98">
-        <v>720.4425445062689</v>
+        <v>720.2628039350053</v>
       </c>
       <c r="E98">
-        <v>448.1759999999999</v>
+        <v>457.3069999999999</v>
       </c>
       <c r="F98">
-        <v>876.5759999999999</v>
+        <v>885.7069999999999</v>
       </c>
       <c r="G98">
         <v>128.8</v>
@@ -9323,28 +9323,28 @@
         <v>147.1</v>
       </c>
       <c r="M98">
-        <v>66.4444608</v>
+        <v>67.13659059999999</v>
       </c>
       <c r="N98">
-        <v>80.65553919999996</v>
+        <v>79.96340939999997</v>
       </c>
       <c r="O98">
-        <v>21.77699558399999</v>
+        <v>21.59012053799999</v>
       </c>
       <c r="P98">
-        <v>58.87854361599997</v>
+        <v>58.37328886199998</v>
       </c>
       <c r="Q98">
-        <v>86.27854361599996</v>
+        <v>85.77328886199997</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>0.6182375445317606</v>
+        <v>0.8062682354551702</v>
       </c>
       <c r="T98">
-        <v>10.48439465986121</v>
+        <v>13.92824279777458</v>
       </c>
       <c r="U98">
         <v>0.07580000000000001</v>
@@ -9361,7 +9361,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>2.213879053707362</v>
+        <v>2.191055558308318</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9369,22 +9369,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.07786202706365514</v>
+        <v>0.07787391234603981</v>
       </c>
       <c r="C99">
-        <v>-36.6441960649945</v>
+        <v>-45.95484697299423</v>
       </c>
       <c r="D99">
-        <v>720.2628039350053</v>
+        <v>720.0831530270057</v>
       </c>
       <c r="E99">
-        <v>457.3069999999999</v>
+        <v>466.4379999999999</v>
       </c>
       <c r="F99">
-        <v>885.7069999999999</v>
+        <v>894.8379999999999</v>
       </c>
       <c r="G99">
         <v>128.8</v>
@@ -9405,28 +9405,28 @@
         <v>147.1</v>
       </c>
       <c r="M99">
-        <v>67.13659059999999</v>
+        <v>67.82872039999999</v>
       </c>
       <c r="N99">
-        <v>79.96340939999997</v>
+        <v>79.27127959999997</v>
       </c>
       <c r="O99">
-        <v>21.59012053799999</v>
+        <v>21.40324549199999</v>
       </c>
       <c r="P99">
-        <v>58.37328886199998</v>
+        <v>57.86803410799997</v>
       </c>
       <c r="Q99">
-        <v>85.77328886199997</v>
+        <v>85.26803410799997</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>0.8062682354551702</v>
+        <v>1.182329617301989</v>
       </c>
       <c r="T99">
-        <v>13.92824279777458</v>
+        <v>20.81593907360132</v>
       </c>
       <c r="U99">
         <v>0.07580000000000001</v>
@@ -9443,7 +9443,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>2.191055558308318</v>
+        <v>2.168697848529662</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9451,22 +9451,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.07787391234603981</v>
+        <v>0.07788579762842449</v>
       </c>
       <c r="C100">
-        <v>-45.95484697299423</v>
+        <v>-55.26540828480609</v>
       </c>
       <c r="D100">
-        <v>720.0831530270057</v>
+        <v>719.9035917151939</v>
       </c>
       <c r="E100">
-        <v>466.4379999999999</v>
+        <v>475.569</v>
       </c>
       <c r="F100">
-        <v>894.8379999999999</v>
+        <v>903.9689999999999</v>
       </c>
       <c r="G100">
         <v>128.8</v>
@@ -9487,28 +9487,28 @@
         <v>147.1</v>
       </c>
       <c r="M100">
-        <v>67.82872039999999</v>
+        <v>68.5208502</v>
       </c>
       <c r="N100">
-        <v>79.27127959999997</v>
+        <v>78.57914979999997</v>
       </c>
       <c r="O100">
-        <v>21.40324549199999</v>
+        <v>21.21637044599999</v>
       </c>
       <c r="P100">
-        <v>57.86803410799997</v>
+        <v>57.36277935399998</v>
       </c>
       <c r="Q100">
-        <v>85.26803410799997</v>
+        <v>84.76277935399997</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>1.182329617301989</v>
+        <v>2.310513762842446</v>
       </c>
       <c r="T100">
-        <v>20.81593907360132</v>
+        <v>41.47902790108157</v>
       </c>
       <c r="U100">
         <v>0.07580000000000001</v>
@@ -9525,91 +9525,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>2.168697848529662</v>
+        <v>2.146791809655625</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.07788579762842449</v>
-      </c>
-      <c r="C101">
-        <v>-55.26540828480609</v>
-      </c>
-      <c r="D101">
-        <v>719.9035917151939</v>
-      </c>
-      <c r="E101">
-        <v>475.569</v>
-      </c>
-      <c r="F101">
-        <v>903.9689999999999</v>
-      </c>
-      <c r="G101">
-        <v>128.8</v>
-      </c>
-      <c r="H101">
-        <v>484.7</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>174.5</v>
-      </c>
-      <c r="K101">
-        <v>27.39999999999999</v>
-      </c>
-      <c r="L101">
-        <v>147.1</v>
-      </c>
-      <c r="M101">
-        <v>68.5208502</v>
-      </c>
-      <c r="N101">
-        <v>78.57914979999997</v>
-      </c>
-      <c r="O101">
-        <v>21.21637044599999</v>
-      </c>
-      <c r="P101">
-        <v>57.36277935399998</v>
-      </c>
-      <c r="Q101">
-        <v>84.76277935399997</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>2.310513762842446</v>
-      </c>
-      <c r="T101">
-        <v>41.47902790108157</v>
-      </c>
-      <c r="U101">
-        <v>0.07580000000000001</v>
-      </c>
-      <c r="V101">
-        <v>0.27</v>
-      </c>
-      <c r="W101">
-        <v>0.055334</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>B2/B</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>2.146791809655625</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
